--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G54">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G56">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G58">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G69">

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G12">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41">

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G57">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G69">

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU72"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G55">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G66">
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 21:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 22:00:00</t>
         </is>
       </c>
     </row>
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G69">
@@ -11659,495 +11659,6 @@
         <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70">
-        <v>0</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <v>0</v>
-      </c>
-      <c r="AC71">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>0</v>
-      </c>
-      <c r="AE71">
-        <v>0</v>
-      </c>
-      <c r="AF71">
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>0</v>
-      </c>
-      <c r="AK71">
-        <v>0</v>
-      </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>2026-07-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>0</v>
-      </c>
-      <c r="AF72">
-        <v>0</v>
-      </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>0</v>
-      </c>
-      <c r="AK72">
-        <v>0</v>
-      </c>
-      <c r="AL72">
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <v>-1</v>
-      </c>
-      <c r="AN72">
-        <v>-1</v>
-      </c>
-      <c r="AO72">
-        <v>-1</v>
-      </c>
-      <c r="AP72">
-        <v>-1</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>0</v>
-      </c>
-      <c r="AT72">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
         <is>
           <t>2026-07-31 23:00:00</t>
         </is>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51">

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-07-31 10:30:00</t>
+          <t>2026-07-31 12:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-07-31 12:00:00</t>
+          <t>2026-07-31 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-31 12:30:00</t>
+          <t>2026-07-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G6">
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-07-31 13:00:00</t>
+          <t>2026-07-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-31 13:30:00</t>
+          <t>2026-07-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-07-31 14:00:00</t>
+          <t>2026-07-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="O25">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>5.12</v>
+        <v>3.99</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P26">
-        <v>3.99</v>
+        <v>2.19</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="O27">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-07-31 14:30:00</t>
+          <t>2026-07-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-07-31 15:00:00</t>
+          <t>2026-07-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-07-31 15:15:00</t>
+          <t>2026-07-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G64">
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 21:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,27 +11020,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 22:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G67">
@@ -11333,332 +11333,6 @@
         <v>0</v>
       </c>
       <c r="AU67" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>2026-07-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-07-31 23:00:00</t>
         </is>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q35">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G51">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 22:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G65">
@@ -11007,332 +11007,6 @@
         <v>0</v>
       </c>
       <c r="AU65" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>-1</v>
-      </c>
-      <c r="AN66">
-        <v>-1</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>-1</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>2026-07-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
         <is>
           <t>2026-07-31 23:00:00</t>
         </is>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G62">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC64">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -970,55 +970,55 @@
         <v>3.46</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.36</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>3.58</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>4.4</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q20">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU65"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,55 +1133,55 @@
         <v>4.09</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>1.62</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>4.73</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA16">
         <v>1.81</v>
@@ -2962,19 +2962,19 @@
         <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.47</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>5.12</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA24">
         <v>1.77</v>
@@ -4266,19 +4266,19 @@
         <v>1.96</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>3.99</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,65 +4547,65 @@
         </is>
       </c>
       <c r="N26">
+        <v>2.26</v>
+      </c>
+      <c r="O26">
+        <v>3.5</v>
+      </c>
+      <c r="P26">
+        <v>2.87</v>
+      </c>
+      <c r="Q26">
+        <v>2.63</v>
+      </c>
+      <c r="R26">
+        <v>2.4</v>
+      </c>
+      <c r="S26">
+        <v>1.23</v>
+      </c>
+      <c r="T26">
+        <v>3.42</v>
+      </c>
+      <c r="U26">
+        <v>2.16</v>
+      </c>
+      <c r="V26">
+        <v>1.65</v>
+      </c>
+      <c r="W26">
+        <v>1.13</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
+        <v>1.11</v>
+      </c>
+      <c r="Z26">
+        <v>5.34</v>
+      </c>
+      <c r="AA26">
+        <v>1.44</v>
+      </c>
+      <c r="AB26">
+        <v>2.42</v>
+      </c>
+      <c r="AC26">
+        <v>2.17</v>
+      </c>
+      <c r="AD26">
+        <v>1.65</v>
+      </c>
+      <c r="AE26">
+        <v>1.26</v>
+      </c>
+      <c r="AF26">
+        <v>1.41</v>
+      </c>
+      <c r="AG26">
         <v>2.66</v>
       </c>
-      <c r="O26">
-        <v>4.1</v>
-      </c>
-      <c r="P26">
-        <v>2.19</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P27">
-        <v>2.87</v>
+        <v>2.19</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5371,34 +5371,34 @@
         <v>3.91</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA31">
         <v>2</v>
@@ -5407,19 +5407,19 @@
         <v>1.78</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>2.37</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G60">
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 22:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G63">
@@ -10681,332 +10681,6 @@
         <v>0</v>
       </c>
       <c r="AU63" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64">
-        <v>2.03</v>
-      </c>
-      <c r="O64">
-        <v>3.28</v>
-      </c>
-      <c r="P64">
-        <v>3.31</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>1.84</v>
-      </c>
-      <c r="AB64">
-        <v>1.83</v>
-      </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>2026-07-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
         <is>
           <t>2026-07-31 23:00:00</t>
         </is>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -1296,55 +1296,55 @@
         <v>2.45</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G17">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.77</v>
+        <v>2.66</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>3.99</v>
+        <v>2.19</v>
       </c>
       <c r="Q25">
-        <v>2.26</v>
+        <v>2.96</v>
       </c>
       <c r="R25">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U25">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
-        <v>5.07</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB25">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="AC25">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AD25">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF25">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AG25">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
+        <v>1.77</v>
+      </c>
+      <c r="O26">
+        <v>3.9</v>
+      </c>
+      <c r="P26">
+        <v>3.99</v>
+      </c>
+      <c r="Q26">
         <v>2.26</v>
       </c>
-      <c r="O26">
+      <c r="R26">
+        <v>2.36</v>
+      </c>
+      <c r="S26">
+        <v>1.22</v>
+      </c>
+      <c r="T26">
         <v>3.5</v>
       </c>
-      <c r="P26">
-        <v>2.87</v>
-      </c>
-      <c r="Q26">
-        <v>2.63</v>
-      </c>
-      <c r="R26">
-        <v>2.4</v>
-      </c>
-      <c r="S26">
-        <v>1.23</v>
-      </c>
-      <c r="T26">
-        <v>3.42</v>
-      </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>5.34</v>
+        <v>5.07</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AC26">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AD26">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE26">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AG26">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="O27">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="Q27">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
         <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="AA27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD27">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE27">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF27">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5860,34 +5860,34 @@
         <v>2.27</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA34">
         <v>1.68</v>
@@ -5896,19 +5896,19 @@
         <v>2.05</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>5.65</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.78</v>
+        <v>7.49</v>
       </c>
       <c r="O37">
-        <v>3.22</v>
+        <v>4.25</v>
       </c>
       <c r="P37">
-        <v>2.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA37">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AB37">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.47</v>
+        <v>1.59</v>
       </c>
       <c r="O38">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>2.5</v>
+        <v>4.67</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>7.49</v>
+        <v>2.78</v>
       </c>
       <c r="O39">
-        <v>4.25</v>
+        <v>3.22</v>
       </c>
       <c r="P39">
-        <v>1.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="O40">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P40">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AA40">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB40">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="P41">
-        <v>4.67</v>
+        <v>2.88</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>1.82</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>8.050000000000001</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
         <v>2.2</v>
@@ -8142,34 +8142,34 @@
         <v>4.51</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA48">
         <v>1.71</v>
@@ -8178,19 +8178,19 @@
         <v>2</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>2.91</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="O39">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="P39">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R39">
         <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG39">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="O40">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="P40">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q40">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="R40">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U40">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z40">
-        <v>4.41</v>
+        <v>3.45</v>
       </c>
       <c r="AA40">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB40">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC40">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="O41">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P41">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
         <v>1.04</v>
       </c>
-      <c r="X41">
-        <v>1.06</v>
-      </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.3</v>
+        <v>4.41</v>
       </c>
       <c r="AA41">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC41">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="O39">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P39">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Q39">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
         <v>1.04</v>
       </c>
-      <c r="X39">
-        <v>1.06</v>
-      </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>3.3</v>
+        <v>4.41</v>
       </c>
       <c r="AA39">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC39">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="O40">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="P40">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="Q40">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R40">
         <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB40">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AC40">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="O41">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q41">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="R41">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z41">
-        <v>4.41</v>
+        <v>3.45</v>
       </c>
       <c r="AA41">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB41">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC41">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE41">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T2">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="U2">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="V2">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W2">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>4.53</v>
+        <v>5</v>
       </c>
       <c r="AA2">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AB2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC2">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="AD2">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG2">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>4.3</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>1.22</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.05</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC63">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
       <c r="O4">
-        <v>3.18</v>
+        <v>3.48</v>
       </c>
       <c r="P4">
-        <v>3.46</v>
+        <v>4.6</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="R4">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="S4">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
         <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="AA4">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AB4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="AD4">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P5">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="Q5">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
         <v>2.31</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="AA5">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB5">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AC5">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
         <v>3.08</v>
       </c>
       <c r="P12">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
+        <v>1.38</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.28</v>
+      </c>
+      <c r="AA12">
+        <v>1.95</v>
+      </c>
+      <c r="AB12">
+        <v>1.74</v>
+      </c>
+      <c r="AC12">
+        <v>3.3</v>
+      </c>
+      <c r="AD12">
+        <v>1.27</v>
+      </c>
+      <c r="AE12">
+        <v>1.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.72</v>
+      </c>
+      <c r="AG12">
+        <v>2.03</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.25</v>
+      </c>
+      <c r="AK12">
         <v>1.36</v>
-      </c>
-      <c r="W12">
-        <v>1.04</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.24</v>
-      </c>
-      <c r="Z12">
-        <v>3.34</v>
-      </c>
-      <c r="AA12">
-        <v>1.9</v>
-      </c>
-      <c r="AB12">
-        <v>1.85</v>
-      </c>
-      <c r="AC12">
-        <v>3.08</v>
-      </c>
-      <c r="AD12">
-        <v>1.28</v>
-      </c>
-      <c r="AE12">
-        <v>1.11</v>
-      </c>
-      <c r="AF12">
-        <v>1.68</v>
-      </c>
-      <c r="AG12">
-        <v>2.06</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.33</v>
-      </c>
-      <c r="AK12">
-        <v>1.34</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3258,16 +3258,16 @@
         <v>2.75</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="V18">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.13</v>
@@ -3282,16 +3282,16 @@
         <v>4.9</v>
       </c>
       <c r="AA18">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB18">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AD18">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE18">
         <v>1.2</v>
@@ -3300,7 +3300,7 @@
         <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P31">
-        <v>3.91</v>
+        <v>4.25</v>
       </c>
       <c r="Q31">
         <v>2.52</v>
@@ -5383,16 +5383,16 @@
         <v>2.54</v>
       </c>
       <c r="U31">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
         <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.36</v>
@@ -5401,19 +5401,19 @@
         <v>2.8</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AB31">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AC31">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="AD31">
         <v>1.19</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>1.93</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="P35">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC35">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G60">

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -647,22 +647,22 @@
         <v>2.3</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S2">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="U2">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="V2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,25 +671,25 @@
         <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA2">
+        <v>1.6</v>
+      </c>
+      <c r="AB2">
+        <v>2.35</v>
+      </c>
+      <c r="AC2">
+        <v>2.48</v>
+      </c>
+      <c r="AD2">
         <v>1.54</v>
       </c>
-      <c r="AB2">
-        <v>2.4</v>
-      </c>
-      <c r="AC2">
-        <v>2.27</v>
-      </c>
-      <c r="AD2">
-        <v>1.49</v>
-      </c>
       <c r="AE2">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG2">
         <v>2.4</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O4">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
         <v>4.6</v>
@@ -997,16 +997,16 @@
         <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AA4">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB4">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>4.13</v>
+        <v>3.9</v>
       </c>
       <c r="AD4">
         <v>1.22</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="P5">
-        <v>4.11</v>
+        <v>4.55</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R5">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1166,16 +1166,16 @@
         <v>1.62</v>
       </c>
       <c r="AB5">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AC5">
         <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
         <v>1.63</v>
@@ -1287,40 +1287,40 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="P6">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V6">
         <v>1.27</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y6">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z6">
         <v>2.8</v>
@@ -1332,19 +1332,19 @@
         <v>1.62</v>
       </c>
       <c r="AC6">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AK6">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
         <v>3.74</v>
       </c>
       <c r="P8">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="Q8">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R8">
         <v>2.35</v>
@@ -1634,13 +1634,13 @@
         <v>4</v>
       </c>
       <c r="U8">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
         <v>1.66</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1655,13 +1655,13 @@
         <v>1.44</v>
       </c>
       <c r="AB8">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC8">
         <v>2.06</v>
       </c>
       <c r="AD8">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE8">
         <v>1.25</v>
@@ -1670,7 +1670,7 @@
         <v>1.4</v>
       </c>
       <c r="AG8">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -2298,10 +2298,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AA12">
         <v>1.95</v>
@@ -2322,7 +2322,7 @@
         <v>1.72</v>
       </c>
       <c r="AG12">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.36</v>
+        <v>3.75</v>
       </c>
       <c r="O13">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="P13">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="R13">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>1.24</v>
       </c>
       <c r="T13">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="U13">
         <v>2.25</v>
@@ -2464,7 +2464,7 @@
         <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
         <v>1.49</v>
@@ -2479,13 +2479,13 @@
         <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P15">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
         <v>2.21</v>
@@ -2778,25 +2778,25 @@
         <v>2.44</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
         <v>2.56</v>
@@ -2811,7 +2811,7 @@
         <v>1.56</v>
       </c>
       <c r="AG15">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
         <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2938,34 +2938,34 @@
         <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
         <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
         <v>4.15</v>
       </c>
       <c r="AA16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC16">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="AD16">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE16">
         <v>1.13</v>
@@ -2974,7 +2974,7 @@
         <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>4.73</v>
       </c>
       <c r="Q17">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="R17">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK17">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R18">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AA18">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC18">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD18">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AG18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="P19">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
+        <v>2.3</v>
+      </c>
+      <c r="S19">
+        <v>1.3</v>
+      </c>
+      <c r="T19">
+        <v>3.1</v>
+      </c>
+      <c r="U19">
         <v>2.4</v>
       </c>
-      <c r="S19">
-        <v>1.25</v>
-      </c>
-      <c r="T19">
-        <v>3.5</v>
-      </c>
-      <c r="U19">
-        <v>2.38</v>
-      </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W19">
         <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>3.92</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AB19">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC19">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD19">
         <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
         <v>2.2</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P22">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="Q22">
         <v>3.62</v>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O24">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>5.12</v>
+        <v>4.8</v>
       </c>
       <c r="Q24">
         <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V24">
         <v>1.47</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4260,22 +4260,22 @@
         <v>3.62</v>
       </c>
       <c r="AA24">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB24">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AC24">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AD24">
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
         <v>2</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
         <v>2.15</v>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="P25">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q25">
         <v>2.96</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
         <v>3.8</v>
@@ -4417,16 +4417,16 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA25">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB25">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AC25">
         <v>2.12</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK25">
         <v>1.42</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P26">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="Q26">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="R26">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
         <v>1.22</v>
@@ -4568,37 +4568,37 @@
         <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V26">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
       <c r="AA26">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AC26">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AD26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF26">
         <v>1.48</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,22 +4710,22 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
         <v>3.42</v>
@@ -4734,7 +4734,7 @@
         <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
         <v>1.13</v>
@@ -4749,10 +4749,10 @@
         <v>5.34</v>
       </c>
       <c r="AA27">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB27">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AC27">
         <v>2.17</v>
@@ -4761,13 +4761,13 @@
         <v>1.65</v>
       </c>
       <c r="AE27">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
         <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
         <v>1.67</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,28 +5039,28 @@
         <v>2.56</v>
       </c>
       <c r="O29">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>3.26</v>
+        <v>2.9</v>
       </c>
       <c r="R29">
         <v>1.84</v>
       </c>
       <c r="S29">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
         <v>1.04</v>
@@ -5081,16 +5081,16 @@
         <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>3.34</v>
+        <v>3.83</v>
       </c>
       <c r="AD29">
         <v>1.24</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG29">
         <v>1.83</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O31">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P31">
         <v>4.25</v>
@@ -5395,10 +5395,10 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AA31">
         <v>2.16</v>
@@ -5416,10 +5416,10 @@
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="O33">
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="R33">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
         <v>3</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA33">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC33">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,61 +5851,61 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="O34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>2.27</v>
       </c>
       <c r="Q34">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
         <v>3.95</v>
       </c>
       <c r="AA34">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB34">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG34">
         <v>2.3</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK34">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="O35">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>5.66</v>
+        <v>5.25</v>
       </c>
       <c r="O45">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -8302,7 +8302,7 @@
         <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q49">
         <v>3.15</v>
@@ -8311,49 +8311,49 @@
         <v>2.2</v>
       </c>
       <c r="S49">
+        <v>1.36</v>
+      </c>
+      <c r="T49">
+        <v>2.88</v>
+      </c>
+      <c r="U49">
+        <v>2.85</v>
+      </c>
+      <c r="V49">
         <v>1.38</v>
       </c>
-      <c r="T49">
-        <v>2.77</v>
-      </c>
-      <c r="U49">
-        <v>2.73</v>
-      </c>
-      <c r="V49">
-        <v>1.39</v>
-      </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA49">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AD49">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8794,25 +8794,25 @@
         <v>2.91</v>
       </c>
       <c r="Q52">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
         <v>1.28</v>
       </c>
       <c r="T52">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V52">
         <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -8824,25 +8824,25 @@
         <v>4</v>
       </c>
       <c r="AA52">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AB52">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC52">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE52">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
         <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK52">
         <v>1.53</v>
@@ -10584,7 +10584,7 @@
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q63">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU63"/>
+  <dimension ref="A1:AU57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="O15">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="Q15">
+        <v>2.59</v>
+      </c>
+      <c r="R15">
+        <v>2.22</v>
+      </c>
+      <c r="S15">
+        <v>1.28</v>
+      </c>
+      <c r="T15">
+        <v>3.25</v>
+      </c>
+      <c r="U15">
         <v>2.5</v>
       </c>
-      <c r="R15">
-        <v>2.21</v>
-      </c>
-      <c r="S15">
-        <v>1.3</v>
-      </c>
-      <c r="T15">
-        <v>3.16</v>
-      </c>
-      <c r="U15">
-        <v>2.44</v>
-      </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA15">
         <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC15">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>2.7</v>
+        <v>4.73</v>
       </c>
       <c r="Q16">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
         <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.15</v>
+        <v>3.96</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB16">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AC16">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AD16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK16">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.51</v>
+        <v>2.09</v>
       </c>
       <c r="O17">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="P17">
-        <v>4.73</v>
+        <v>3.17</v>
       </c>
       <c r="Q17">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="P20">
-        <v>4.3</v>
+        <v>4.81</v>
       </c>
       <c r="Q20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>5.23</v>
+        <v>5.72</v>
       </c>
       <c r="AA20">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AB20">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AC20">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AD20">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AE20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4882,10 +4882,10 @@
         <v>4.25</v>
       </c>
       <c r="Q28">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R28">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
         <v>1.37</v>
@@ -4912,19 +4912,19 @@
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB28">
         <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
         <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
         <v>1.82</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.56</v>
+        <v>1.15</v>
       </c>
       <c r="O29">
+        <v>6.75</v>
+      </c>
+      <c r="P29">
+        <v>11.5</v>
+      </c>
+      <c r="Q29">
+        <v>1.57</v>
+      </c>
+      <c r="R29">
         <v>3</v>
       </c>
-      <c r="P29">
-        <v>2.75</v>
-      </c>
-      <c r="Q29">
+      <c r="S29">
+        <v>1.17</v>
+      </c>
+      <c r="T29">
+        <v>4.5</v>
+      </c>
+      <c r="U29">
+        <v>2.06</v>
+      </c>
+      <c r="V29">
+        <v>1.72</v>
+      </c>
+      <c r="W29">
+        <v>1.18</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.08</v>
+      </c>
+      <c r="Z29">
+        <v>6.5</v>
+      </c>
+      <c r="AA29">
+        <v>1.36</v>
+      </c>
+      <c r="AB29">
         <v>2.9</v>
       </c>
-      <c r="R29">
-        <v>1.84</v>
-      </c>
-      <c r="S29">
-        <v>1.43</v>
-      </c>
-      <c r="T29">
-        <v>2.75</v>
-      </c>
-      <c r="U29">
-        <v>3.2</v>
-      </c>
-      <c r="V29">
-        <v>1.3</v>
-      </c>
-      <c r="W29">
-        <v>1.04</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>1.34</v>
-      </c>
-      <c r="Z29">
-        <v>3.08</v>
-      </c>
-      <c r="AA29">
-        <v>2.21</v>
-      </c>
-      <c r="AB29">
-        <v>1.65</v>
-      </c>
       <c r="AC29">
-        <v>3.83</v>
+        <v>2.01</v>
       </c>
       <c r="AD29">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AF29">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-07-31 15:15:00</t>
+          <t>2026-07-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-07-31 15:30:00</t>
+          <t>2026-07-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U34">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="V34">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AA34">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC34">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD34">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="O35">
+        <v>3.4</v>
+      </c>
+      <c r="P35">
+        <v>2.27</v>
+      </c>
+      <c r="Q35">
         <v>3.25</v>
       </c>
-      <c r="P35">
-        <v>2.1</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA35">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="O36">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>5.65</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-07-31 15:45:00</t>
+          <t>2026-07-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>7.49</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>1.37</v>
+        <v>5.75</v>
       </c>
       <c r="Q37">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="R37">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
+        <v>1.13</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.13</v>
+      </c>
+      <c r="Z37">
+        <v>4.75</v>
+      </c>
+      <c r="AA37">
+        <v>1.53</v>
+      </c>
+      <c r="AB37">
+        <v>2.28</v>
+      </c>
+      <c r="AC37">
+        <v>2.3</v>
+      </c>
+      <c r="AD37">
+        <v>1.57</v>
+      </c>
+      <c r="AE37">
+        <v>1.21</v>
+      </c>
+      <c r="AF37">
+        <v>1.67</v>
+      </c>
+      <c r="AG37">
+        <v>2.08</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.1</v>
       </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>1.12</v>
-      </c>
-      <c r="Z37">
-        <v>3.95</v>
-      </c>
-      <c r="AA37">
-        <v>1.58</v>
-      </c>
-      <c r="AB37">
-        <v>2.1</v>
-      </c>
-      <c r="AC37">
-        <v>2.5</v>
-      </c>
-      <c r="AD37">
-        <v>1.43</v>
-      </c>
-      <c r="AE37">
-        <v>1.15</v>
-      </c>
-      <c r="AF37">
-        <v>1.83</v>
-      </c>
-      <c r="AG37">
-        <v>1.86</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.13</v>
-      </c>
       <c r="AK37">
-        <v>1.05</v>
+        <v>2.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.59</v>
+        <v>4.66</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>4.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.47</v>
+        <v>10.4</v>
       </c>
       <c r="O39">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="P39">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q39">
-        <v>2.89</v>
+        <v>7</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S39">
         <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U39">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>4.41</v>
+        <v>3.95</v>
       </c>
       <c r="AA39">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AB39">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD39">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE39">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>3.5</v>
       </c>
       <c r="AK39">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="O40">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="P41">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="Q41">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA41">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AB41">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AC41">
-        <v>2.85</v>
+        <v>3.37</v>
       </c>
       <c r="AD41">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-07-31 16:00:00</t>
+          <t>2026-07-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.3</v>
+      </c>
+      <c r="O43">
+        <v>3.4</v>
+      </c>
+      <c r="P43">
+        <v>2.7</v>
+      </c>
+      <c r="Q43">
+        <v>2.95</v>
+      </c>
+      <c r="R43">
+        <v>2.13</v>
+      </c>
+      <c r="S43">
+        <v>1.3</v>
+      </c>
+      <c r="T43">
+        <v>3.25</v>
+      </c>
+      <c r="U43">
+        <v>2.28</v>
+      </c>
+      <c r="V43">
+        <v>1.55</v>
+      </c>
+      <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.16</v>
+      </c>
+      <c r="Z43">
         <v>4.2</v>
       </c>
-      <c r="O43">
-        <v>3.5</v>
-      </c>
-      <c r="P43">
-        <v>1.82</v>
-      </c>
-      <c r="Q43">
-        <v>4.75</v>
-      </c>
-      <c r="R43">
-        <v>2.06</v>
-      </c>
-      <c r="S43">
-        <v>1.41</v>
-      </c>
-      <c r="T43">
-        <v>2.69</v>
-      </c>
-      <c r="U43">
-        <v>2.94</v>
-      </c>
-      <c r="V43">
-        <v>1.35</v>
-      </c>
-      <c r="W43">
-        <v>1.06</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43">
-        <v>1.27</v>
-      </c>
-      <c r="Z43">
-        <v>3.18</v>
-      </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AC43">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD43">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AG43">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-07-31 16:00:00</t>
+          <t>2026-07-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>8.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>5.25</v>
+        <v>1.28</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="P45">
-        <v>1.53</v>
+        <v>7</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="AA45">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AB45">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC45">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AD45">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7760,22 +7760,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,16 +7846,16 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00:00</t>
+          <t>2026-07-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-07-31 20:00:00</t>
+          <t>2026-07-31 18:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-07-31 20:30:00</t>
+          <t>2026-07-31 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,68 +8455,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AB51">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,68 +8781,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-07-31 21:00:00</t>
+          <t>2026-07-31 22:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9703,984 +9703,6 @@
         <v>0</v>
       </c>
       <c r="AU57" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
-      </c>
-      <c r="AB58">
-        <v>0</v>
-      </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>0</v>
-      </c>
-      <c r="AF58">
-        <v>0</v>
-      </c>
-      <c r="AG58">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>0</v>
-      </c>
-      <c r="AK58">
-        <v>0</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>-1</v>
-      </c>
-      <c r="AN58">
-        <v>-1</v>
-      </c>
-      <c r="AO58">
-        <v>-1</v>
-      </c>
-      <c r="AP58">
-        <v>-1</v>
-      </c>
-      <c r="AQ58">
-        <v>0</v>
-      </c>
-      <c r="AR58">
-        <v>0</v>
-      </c>
-      <c r="AS58">
-        <v>0</v>
-      </c>
-      <c r="AT58">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
-      <c r="W59">
-        <v>0</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>0</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
-      <c r="AD59">
-        <v>0</v>
-      </c>
-      <c r="AE59">
-        <v>0</v>
-      </c>
-      <c r="AF59">
-        <v>0</v>
-      </c>
-      <c r="AG59">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>0</v>
-      </c>
-      <c r="AK59">
-        <v>0</v>
-      </c>
-      <c r="AL59">
-        <v>0</v>
-      </c>
-      <c r="AM59">
-        <v>-1</v>
-      </c>
-      <c r="AN59">
-        <v>-1</v>
-      </c>
-      <c r="AO59">
-        <v>-1</v>
-      </c>
-      <c r="AP59">
-        <v>-1</v>
-      </c>
-      <c r="AQ59">
-        <v>0</v>
-      </c>
-      <c r="AR59">
-        <v>0</v>
-      </c>
-      <c r="AS59">
-        <v>0</v>
-      </c>
-      <c r="AT59">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>0</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60">
-        <v>0</v>
-      </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
-      </c>
-      <c r="X60">
-        <v>0</v>
-      </c>
-      <c r="Y60">
-        <v>0</v>
-      </c>
-      <c r="Z60">
-        <v>0</v>
-      </c>
-      <c r="AA60">
-        <v>0</v>
-      </c>
-      <c r="AB60">
-        <v>0</v>
-      </c>
-      <c r="AC60">
-        <v>0</v>
-      </c>
-      <c r="AD60">
-        <v>0</v>
-      </c>
-      <c r="AE60">
-        <v>0</v>
-      </c>
-      <c r="AF60">
-        <v>0</v>
-      </c>
-      <c r="AG60">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>0</v>
-      </c>
-      <c r="AK60">
-        <v>0</v>
-      </c>
-      <c r="AL60">
-        <v>0</v>
-      </c>
-      <c r="AM60">
-        <v>-1</v>
-      </c>
-      <c r="AN60">
-        <v>-1</v>
-      </c>
-      <c r="AO60">
-        <v>-1</v>
-      </c>
-      <c r="AP60">
-        <v>-1</v>
-      </c>
-      <c r="AQ60">
-        <v>0</v>
-      </c>
-      <c r="AR60">
-        <v>0</v>
-      </c>
-      <c r="AS60">
-        <v>0</v>
-      </c>
-      <c r="AT60">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Deportes Iquique</t>
-        </is>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>0</v>
-      </c>
-      <c r="AB61">
-        <v>0</v>
-      </c>
-      <c r="AC61">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61">
-        <v>0</v>
-      </c>
-      <c r="AF61">
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>0</v>
-      </c>
-      <c r="AK61">
-        <v>0</v>
-      </c>
-      <c r="AL61">
-        <v>0</v>
-      </c>
-      <c r="AM61">
-        <v>-1</v>
-      </c>
-      <c r="AN61">
-        <v>-1</v>
-      </c>
-      <c r="AO61">
-        <v>-1</v>
-      </c>
-      <c r="AP61">
-        <v>-1</v>
-      </c>
-      <c r="AQ61">
-        <v>0</v>
-      </c>
-      <c r="AR61">
-        <v>0</v>
-      </c>
-      <c r="AS61">
-        <v>0</v>
-      </c>
-      <c r="AT61">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>2026-07-31 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N62">
-        <v>2.03</v>
-      </c>
-      <c r="O62">
-        <v>3.28</v>
-      </c>
-      <c r="P62">
-        <v>3.31</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <v>1.84</v>
-      </c>
-      <c r="AB62">
-        <v>1.83</v>
-      </c>
-      <c r="AC62">
-        <v>0</v>
-      </c>
-      <c r="AD62">
-        <v>0</v>
-      </c>
-      <c r="AE62">
-        <v>0</v>
-      </c>
-      <c r="AF62">
-        <v>0</v>
-      </c>
-      <c r="AG62">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>0</v>
-      </c>
-      <c r="AK62">
-        <v>0</v>
-      </c>
-      <c r="AL62">
-        <v>0</v>
-      </c>
-      <c r="AM62">
-        <v>-1</v>
-      </c>
-      <c r="AN62">
-        <v>-1</v>
-      </c>
-      <c r="AO62">
-        <v>-1</v>
-      </c>
-      <c r="AP62">
-        <v>-1</v>
-      </c>
-      <c r="AQ62">
-        <v>0</v>
-      </c>
-      <c r="AR62">
-        <v>0</v>
-      </c>
-      <c r="AS62">
-        <v>0</v>
-      </c>
-      <c r="AT62">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>2026-07-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N63">
-        <v>2.49</v>
-      </c>
-      <c r="O63">
-        <v>3.6</v>
-      </c>
-      <c r="P63">
-        <v>2.4</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>1.57</v>
-      </c>
-      <c r="AB63">
-        <v>2.35</v>
-      </c>
-      <c r="AC63">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>0</v>
-      </c>
-      <c r="AK63">
-        <v>0</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>-1</v>
-      </c>
-      <c r="AN63">
-        <v>-1</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>-1</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
         <is>
           <t>2026-07-31 23:00:00</t>
         </is>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -644,22 +644,22 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R2">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,28 +668,28 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z2">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA2">
         <v>1.6</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC2">
         <v>2.48</v>
       </c>
       <c r="AD2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE2">
         <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG2">
         <v>2.4</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>4.6</v>
+        <v>4.87</v>
       </c>
       <c r="Q4">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
         <v>1.42</v>
@@ -988,28 +988,28 @@
         <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z4">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA4">
         <v>2.23</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
         <v>1.03</v>
@@ -1018,7 +1018,7 @@
         <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         <v>3.95</v>
       </c>
       <c r="P5">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="Q5">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1151,7 +1151,7 @@
         <v>1.51</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,28 +1160,28 @@
         <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
         <v>1.62</v>
       </c>
       <c r="AB5">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AC5">
         <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
         <v>2.1</v>
@@ -1296,28 +1296,28 @@
         <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
         <v>1.01</v>
       </c>
       <c r="X6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
         <v>1.37</v>
@@ -1335,16 +1335,16 @@
         <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1483,31 +1483,31 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1634,13 +1634,13 @@
         <v>4</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V8">
         <v>1.66</v>
       </c>
       <c r="W8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1664,7 +1664,7 @@
         <v>1.68</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF8">
         <v>1.4</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
         <v>1.76</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="P12">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="R12">
         <v>2.1</v>
@@ -2283,7 +2283,7 @@
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U12">
         <v>2.77</v>
@@ -2292,7 +2292,7 @@
         <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2301,28 +2301,28 @@
         <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AA12">
         <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
         <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK12">
         <v>1.36</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
         <v>3.92</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
         <v>4.22</v>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>3.35</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P14">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,28 +2754,28 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O15">
         <v>3.6</v>
       </c>
       <c r="P15">
+        <v>2.8</v>
+      </c>
+      <c r="Q15">
         <v>2.7</v>
       </c>
-      <c r="Q15">
-        <v>2.59</v>
-      </c>
       <c r="R15">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V15">
         <v>1.5</v>
@@ -2787,22 +2787,22 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB15">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC15">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
         <v>1.13</v>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>4.73</v>
       </c>
       <c r="Q16">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2941,19 +2941,19 @@
         <v>2.47</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.96</v>
+        <v>4.09</v>
       </c>
       <c r="AA16">
         <v>1.69</v>
@@ -2962,19 +2962,19 @@
         <v>2.11</v>
       </c>
       <c r="AC16">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.62</v>
@@ -3083,7 +3083,7 @@
         <v>2.09</v>
       </c>
       <c r="O17">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
         <v>3.17</v>
@@ -3092,16 +3092,16 @@
         <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
         <v>1.48</v>
@@ -3110,19 +3110,19 @@
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC17">
         <v>2.56</v>
@@ -3131,13 +3131,13 @@
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3282,16 +3282,16 @@
         <v>5.2</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB18">
         <v>2.45</v>
       </c>
       <c r="AC18">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AD18">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE18">
         <v>1.24</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK18">
         <v>4.33</v>
@@ -3418,28 +3418,28 @@
         <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
         <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
         <v>1.48</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
         <v>3.92</v>
@@ -3448,19 +3448,19 @@
         <v>1.68</v>
       </c>
       <c r="AB19">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
         <v>2.2</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O20">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="P20">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
         <v>2.45</v>
@@ -3590,34 +3590,34 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W20">
         <v>1.17</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>5.72</v>
+        <v>5.35</v>
       </c>
       <c r="AA20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AC20">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE20">
         <v>1.22</v>
@@ -3642,7 +3642,7 @@
         <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="P22">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>3.62</v>
+        <v>3.88</v>
       </c>
       <c r="R22">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U22">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.03</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.32</v>
@@ -3934,13 +3934,13 @@
         <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB22">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC22">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="AD22">
         <v>1.24</v>
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="P24">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4242,7 +4242,7 @@
         <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
         <v>1.47</v>
@@ -4275,10 +4275,10 @@
         <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4387,19 +4387,19 @@
         <v>2.48</v>
       </c>
       <c r="O25">
-        <v>3.78</v>
+        <v>4.09</v>
       </c>
       <c r="P25">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q25">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R25">
         <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T25">
         <v>3.8</v>
@@ -4420,7 +4420,7 @@
         <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
         <v>1.41</v>
@@ -4550,7 +4550,7 @@
         <v>1.68</v>
       </c>
       <c r="O26">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
         <v>3.95</v>
@@ -4568,13 +4568,13 @@
         <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
         <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4592,19 +4592,19 @@
         <v>2.41</v>
       </c>
       <c r="AC26">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AD26">
         <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
         <v>1.48</v>
       </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
         <v>1.97</v>
@@ -4713,13 +4713,13 @@
         <v>2.18</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
         <v>2.31</v>
@@ -4746,16 +4746,16 @@
         <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.34</v>
+        <v>4.9</v>
       </c>
       <c r="AA27">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AC27">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD27">
         <v>1.65</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
         <v>1.67</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P28">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
       <c r="Q28">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.04</v>
@@ -4906,31 +4906,31 @@
         <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,22 +5045,22 @@
         <v>11.5</v>
       </c>
       <c r="Q29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V29">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W29">
         <v>1.18</v>
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>6.5</v>
+        <v>5.82</v>
       </c>
       <c r="AA29">
         <v>1.36</v>
@@ -5081,13 +5081,13 @@
         <v>2.9</v>
       </c>
       <c r="AC29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD29">
         <v>1.82</v>
       </c>
       <c r="AE29">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF29">
         <v>1.81</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="O32">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q32">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="R32">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="U32">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="V32">
         <v>1.3</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z32">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AB32">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC32">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5857,28 +5857,28 @@
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
         <v>3.84</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,19 +5887,19 @@
         <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB34">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
         <v>3.7</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="O35">
         <v>3.4</v>
@@ -6023,10 +6023,10 @@
         <v>2.27</v>
       </c>
       <c r="Q35">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
         <v>1.32</v>
@@ -6050,7 +6050,7 @@
         <v>1.23</v>
       </c>
       <c r="Z35">
-        <v>3.95</v>
+        <v>4.28</v>
       </c>
       <c r="AA35">
         <v>1.7</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
         <v>1.36</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P37">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="Q37">
         <v>1.9</v>
@@ -6358,16 +6358,16 @@
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
         <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,7 +6376,7 @@
         <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>4.75</v>
+        <v>5.13</v>
       </c>
       <c r="AA37">
         <v>1.53</v>
@@ -6397,7 +6397,7 @@
         <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.1</v>
       </c>
       <c r="AK37">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.66</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
         <v>3.45</v>
       </c>
       <c r="P38">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q38">
         <v>4.5</v>
@@ -6518,13 +6518,13 @@
         <v>2.1</v>
       </c>
       <c r="S38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="V38">
         <v>1.36</v>
@@ -6533,7 +6533,7 @@
         <v>1.03</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
         <v>1.27</v>
@@ -6557,7 +6557,7 @@
         <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG38">
         <v>1.82</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.94</v>
       </c>
       <c r="AK38">
         <v>1.15</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>10.4</v>
+        <v>7.2</v>
       </c>
       <c r="O39">
         <v>4.75</v>
@@ -6675,22 +6675,22 @@
         <v>1.26</v>
       </c>
       <c r="Q39">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="R39">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="U39">
         <v>2.15</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.1</v>
@@ -6720,7 +6720,7 @@
         <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG39">
         <v>1.85</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6998,10 +6998,10 @@
         <v>3.14</v>
       </c>
       <c r="P41">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="Q41">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R41">
         <v>2.03</v>
@@ -7013,16 +7013,16 @@
         <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
         <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
         <v>1.25</v>
@@ -7037,7 +7037,7 @@
         <v>1.82</v>
       </c>
       <c r="AC41">
-        <v>3.37</v>
+        <v>2.95</v>
       </c>
       <c r="AD41">
         <v>1.3</v>
@@ -7049,7 +7049,7 @@
         <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>2.75</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
         <v>1.33</v>
@@ -7176,10 +7176,10 @@
         <v>2.91</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V42">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
         <v>1.06</v>
@@ -7191,22 +7191,22 @@
         <v>1.23</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="AA42">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AK42">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
         <v>1.07</v>
@@ -7354,22 +7354,22 @@
         <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB43">
         <v>2.18</v>
       </c>
       <c r="AC43">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AD43">
         <v>1.48</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
         <v>1.52</v>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7647,16 +7647,16 @@
         <v>1.28</v>
       </c>
       <c r="O45">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P45">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q45">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R45">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="S45">
         <v>1.18</v>
@@ -7665,10 +7665,10 @@
         <v>4.33</v>
       </c>
       <c r="U45">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V45">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W45">
         <v>1.22</v>
@@ -7677,28 +7677,28 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z45">
-        <v>7.14</v>
+        <v>6.8</v>
       </c>
       <c r="AA45">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AB45">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC45">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD45">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AE45">
         <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
         <v>2.25</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK45">
         <v>3.4</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O51">
         <v>3.3</v>
@@ -8631,7 +8631,7 @@
         <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R51">
         <v>2.2</v>
@@ -8646,7 +8646,7 @@
         <v>2.85</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8661,16 +8661,16 @@
         <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
         <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
         <v>1.07</v>
@@ -8679,7 +8679,7 @@
         <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>2.91</v>
       </c>
       <c r="Q54">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R54">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S54">
         <v>1.28</v>
@@ -9132,10 +9132,10 @@
         <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V54">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
         <v>1.1</v>
@@ -9156,10 +9156,10 @@
         <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
         <v>1.1</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>2.49</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
         <v>2.4</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="Q4">
         <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S4">
         <v>1.42</v>
@@ -1000,13 +1000,13 @@
         <v>2.69</v>
       </c>
       <c r="AA4">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB4">
         <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AD4">
         <v>1.18</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2268,13 +2268,13 @@
         <v>2.75</v>
       </c>
       <c r="O12">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="Q12">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R12">
         <v>2.1</v>
@@ -2283,7 +2283,7 @@
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="U12">
         <v>2.77</v>
@@ -2295,28 +2295,28 @@
         <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
         <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
         <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
         <v>1.73</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.48</v>
+        <v>1.68</v>
       </c>
       <c r="O25">
-        <v>4.09</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="Q25">
-        <v>2.74</v>
+        <v>2.21</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V25">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD25">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE25">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AG25">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.68</v>
+        <v>2.18</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P26">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4583,28 +4583,28 @@
         <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA26">
         <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC26">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AD26">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="O27">
-        <v>3.54</v>
+        <v>4.09</v>
       </c>
       <c r="P27">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T27">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC27">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF27">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG27">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.37</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
         <v>2.29</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
         <v>2.95</v>
@@ -4897,31 +4897,31 @@
         <v>2.9</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
         <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
@@ -4930,7 +4930,7 @@
         <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5525,37 +5525,37 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q32">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="S32">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y32">
         <v>1.39</v>
@@ -5567,22 +5567,22 @@
         <v>2.23</v>
       </c>
       <c r="AB32">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC32">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG32">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P36">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -8468,25 +8468,25 @@
         <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R50">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
         <v>2.6</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>1.04</v>
@@ -8495,25 +8495,25 @@
         <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
         <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC50">
         <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
         <v>1.98</v>
@@ -8951,10 +8951,10 @@
         <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P53">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="Q53">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="O51">
         <v>3.3</v>
@@ -8631,22 +8631,22 @@
         <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
         <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8655,19 +8655,19 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
         <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AD51">
         <v>1.32</v>
@@ -8676,7 +8676,7 @@
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
         <v>2.04</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -810,13 +810,13 @@
         <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
         <v>2.53</v>
@@ -828,7 +828,7 @@
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.2</v>
@@ -855,7 +855,7 @@
         <v>1.61</v>
       </c>
       <c r="AG3">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1794,16 +1794,16 @@
         <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1815,10 +1815,10 @@
         <v>3.42</v>
       </c>
       <c r="AA9">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
         <v>2.92</v>
@@ -1830,10 +1830,10 @@
         <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK9">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1993,10 +1993,10 @@
         <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -4076,19 +4076,19 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
         <v>1.44</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.19</v>
@@ -4097,10 +4097,10 @@
         <v>3.82</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
         <v>2.81</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -650,37 +650,37 @@
         <v>2.45</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T2">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U2">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="V2">
         <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.12</v>
       </c>
       <c r="Z2">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="AA2">
         <v>1.6</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC2">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="AD2">
         <v>1.55</v>
@@ -689,10 +689,10 @@
         <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="R4">
         <v>1.99</v>
       </c>
       <c r="S4">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T4">
         <v>2.5</v>
@@ -985,31 +985,31 @@
         <v>3.16</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
         <v>1.41</v>
       </c>
       <c r="Z4">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AA4">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB4">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
         <v>4</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.03</v>
@@ -1124,22 +1124,22 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O5">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
         <v>3.25</v>
@@ -1157,7 +1157,7 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
         <v>4.33</v>
@@ -1172,7 +1172,7 @@
         <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="P6">
         <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1305,16 +1305,16 @@
         <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
         <v>1.05</v>
@@ -1323,13 +1323,13 @@
         <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC6">
         <v>4.33</v>
@@ -1344,7 +1344,7 @@
         <v>1.96</v>
       </c>
       <c r="AG6">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AK6">
         <v>1.33</v>
@@ -1634,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="U8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
         <v>1.66</v>
@@ -1646,10 +1646,10 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="AA8">
         <v>1.44</v>
@@ -1661,10 +1661,10 @@
         <v>2.06</v>
       </c>
       <c r="AD8">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
         <v>1.4</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="O12">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R12">
         <v>2.1</v>
@@ -2304,13 +2304,13 @@
         <v>3.15</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
         <v>1.27</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK12">
         <v>1.35</v>
@@ -2434,19 +2434,19 @@
         <v>3.92</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
         <v>2.25</v>
@@ -2455,7 +2455,7 @@
         <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,22 +2467,22 @@
         <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AC13">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
         <v>1.18</v>
@@ -2757,16 +2757,16 @@
         <v>2.15</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S15">
         <v>1.28</v>
@@ -2775,19 +2775,19 @@
         <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
         <v>4.2</v>
@@ -2796,10 +2796,10 @@
         <v>1.64</v>
       </c>
       <c r="AB15">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
         <v>1.42</v>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,34 +2926,34 @@
         <v>4.73</v>
       </c>
       <c r="Q16">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="S16">
         <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
         <v>1.49</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
         <v>1.69</v>
@@ -2965,7 +2965,7 @@
         <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
         <v>3.17</v>
@@ -3098,13 +3098,13 @@
         <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
         <v>1.08</v>
@@ -3122,10 +3122,10 @@
         <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3276,31 +3276,31 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA18">
         <v>1.42</v>
       </c>
       <c r="AB18">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AC18">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AD18">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE18">
         <v>1.24</v>
       </c>
       <c r="AF18">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3412,19 +3412,19 @@
         <v>3.82</v>
       </c>
       <c r="P19">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
         <v>2.44</v>
@@ -3442,25 +3442,25 @@
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC19">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD19">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG19">
         <v>2.2</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
         <v>2.1</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O20">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>4.88</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
         <v>2.45</v>
@@ -3590,43 +3590,43 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AA20">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB20">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD20">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
         <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,22 +3895,22 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="O22">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="R22">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
         <v>2.81</v>
@@ -3943,7 +3943,7 @@
         <v>3.68</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AK22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O24">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="P24">
-        <v>4.79</v>
+        <v>4.9</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4245,7 +4245,7 @@
         <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
         <v>1.76</v>
@@ -4272,10 +4272,10 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
         <v>1.95</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P25">
         <v>3.95</v>
       </c>
       <c r="Q25">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
         <v>2.18</v>
@@ -4426,13 +4426,13 @@
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AC25">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AD25">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE25">
         <v>1.2</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="Q26">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="R26">
         <v>2.31</v>
@@ -4568,13 +4568,13 @@
         <v>3.42</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4586,16 +4586,16 @@
         <v>4.9</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB26">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC26">
         <v>2.16</v>
       </c>
       <c r="AD26">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
         <v>1.22</v>
@@ -4604,7 +4604,7 @@
         <v>1.41</v>
       </c>
       <c r="AG26">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="O27">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="P27">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
         <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="U27">
         <v>2.1</v>
@@ -4743,22 +4743,22 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="AA27">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB27">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC27">
         <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE27">
         <v>1.23</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4912,16 +4912,16 @@
         <v>3.2</v>
       </c>
       <c r="AA28">
+        <v>1.95</v>
+      </c>
+      <c r="AB28">
         <v>1.9</v>
-      </c>
-      <c r="AB28">
-        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>3.35</v>
       </c>
       <c r="AD28">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="O29">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="P29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R29">
         <v>3</v>
@@ -5057,43 +5057,43 @@
         <v>4</v>
       </c>
       <c r="U29">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V29">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z29">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="AA29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD29">
+        <v>1.7</v>
+      </c>
+      <c r="AE29">
+        <v>1.29</v>
+      </c>
+      <c r="AF29">
         <v>1.82</v>
       </c>
-      <c r="AE29">
-        <v>1.31</v>
-      </c>
-      <c r="AF29">
-        <v>1.81</v>
-      </c>
       <c r="AG29">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q31">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="R31">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
         <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.74</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
         <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AD31">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
+        <v>1.16</v>
+      </c>
+      <c r="AF31">
+        <v>1.52</v>
+      </c>
+      <c r="AG31">
+        <v>2.25</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.21</v>
       </c>
-      <c r="AF31">
-        <v>1.47</v>
-      </c>
-      <c r="AG31">
-        <v>2.42</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.57</v>
-      </c>
       <c r="AK31">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,31 +5525,31 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O32">
         <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q32">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
         <v>3.32</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W32">
         <v>1.02</v>
@@ -5564,10 +5564,10 @@
         <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AB32">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC32">
         <v>4.05</v>
@@ -5582,23 +5582,23 @@
         <v>1.92</v>
       </c>
       <c r="AG32">
+        <v>1.8</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.24</v>
+      </c>
+      <c r="AK32">
         <v>1.7</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.32</v>
-      </c>
-      <c r="AK32">
-        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5857,13 +5857,13 @@
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
         <v>3.84</v>
       </c>
       <c r="R34">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S34">
         <v>1.44</v>
@@ -5881,7 +5881,7 @@
         <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
         <v>1.3</v>
@@ -5896,10 +5896,10 @@
         <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,25 +6014,25 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S35">
         <v>1.32</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
         <v>2.47</v>
@@ -6047,31 +6047,31 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
         <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
         <v>1.36</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O36">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="O37">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>5.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q37">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="R37">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
+        <v>1.36</v>
+      </c>
+      <c r="T37">
+        <v>2.9</v>
+      </c>
+      <c r="U37">
+        <v>2.88</v>
+      </c>
+      <c r="V37">
+        <v>1.36</v>
+      </c>
+      <c r="W37">
+        <v>1.03</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.27</v>
+      </c>
+      <c r="Z37">
+        <v>3.18</v>
+      </c>
+      <c r="AA37">
+        <v>2</v>
+      </c>
+      <c r="AB37">
+        <v>1.75</v>
+      </c>
+      <c r="AC37">
+        <v>3.3</v>
+      </c>
+      <c r="AD37">
         <v>1.25</v>
       </c>
-      <c r="T37">
-        <v>3.7</v>
-      </c>
-      <c r="U37">
-        <v>2.2</v>
-      </c>
-      <c r="V37">
-        <v>1.59</v>
-      </c>
-      <c r="W37">
-        <v>1.12</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.13</v>
-      </c>
-      <c r="Z37">
-        <v>5.13</v>
-      </c>
-      <c r="AA37">
-        <v>1.53</v>
-      </c>
-      <c r="AB37">
-        <v>2.28</v>
-      </c>
-      <c r="AC37">
-        <v>2.3</v>
-      </c>
-      <c r="AD37">
-        <v>1.57</v>
-      </c>
       <c r="AE37">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="O38">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="P38">
-        <v>1.74</v>
+        <v>6.15</v>
       </c>
       <c r="Q38">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="S38">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T38">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.97</v>
+        <v>2.15</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="W38">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD38">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AE38">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AF38">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.94</v>
+        <v>1.15</v>
       </c>
       <c r="AK38">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>4.75</v>
@@ -6675,10 +6675,10 @@
         <v>1.26</v>
       </c>
       <c r="Q39">
-        <v>7.9</v>
+        <v>8.25</v>
       </c>
       <c r="R39">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
         <v>1.28</v>
@@ -6687,43 +6687,43 @@
         <v>3.18</v>
       </c>
       <c r="U39">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
         <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA39">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AC39">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AD39">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AE39">
         <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AK39">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6995,16 +6995,16 @@
         <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q41">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="R41">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="S41">
         <v>1.38</v>
@@ -7013,13 +7013,13 @@
         <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.05</v>
@@ -7028,10 +7028,10 @@
         <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AA41">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
         <v>1.82</v>
@@ -7040,10 +7040,10 @@
         <v>2.95</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
         <v>1.7</v>
@@ -7065,7 +7065,7 @@
         <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P42">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -7188,31 +7188,31 @@
         <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AK42">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,16 +7321,16 @@
         <v>2.3</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q43">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="S43">
         <v>1.3</v>
@@ -7342,7 +7342,7 @@
         <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W43">
         <v>1.07</v>
@@ -7357,16 +7357,16 @@
         <v>4.15</v>
       </c>
       <c r="AA43">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
         <v>2.18</v>
       </c>
       <c r="AC43">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AD43">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE43">
         <v>1.15</v>
@@ -7375,7 +7375,7 @@
         <v>1.52</v>
       </c>
       <c r="AG43">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O45">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="P45">
         <v>7.5</v>
       </c>
       <c r="Q45">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R45">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="S45">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T45">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U45">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V45">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W45">
         <v>1.22</v>
@@ -7680,28 +7680,28 @@
         <v>1.04</v>
       </c>
       <c r="Z45">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="AA45">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AB45">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC45">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AD45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AE45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF45">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="O46">
         <v>4.4</v>
       </c>
       <c r="P46">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O50">
         <v>4.36</v>
@@ -8468,22 +8468,22 @@
         <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
         <v>1.06</v>
@@ -8498,10 +8498,10 @@
         <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AC50">
         <v>2.8</v>
@@ -8513,10 +8513,10 @@
         <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG50">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S51">
         <v>1.4</v>
@@ -8646,7 +8646,7 @@
         <v>2.8</v>
       </c>
       <c r="V51">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>2.91</v>
       </c>
       <c r="Q54">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R54">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S54">
         <v>1.28</v>
@@ -9135,10 +9135,10 @@
         <v>2.44</v>
       </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9147,10 +9147,10 @@
         <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="AA54">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AB54">
         <v>2.1</v>
@@ -9159,7 +9159,7 @@
         <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
         <v>1.1</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>2.21</v>
       </c>
       <c r="O56">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="P56">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
+        <v>2.4</v>
+      </c>
+      <c r="O57">
+        <v>3.6</v>
+      </c>
+      <c r="P57">
         <v>2.49</v>
-      </c>
-      <c r="O57">
-        <v>3.5</v>
-      </c>
-      <c r="P57">
-        <v>2.4</v>
       </c>
       <c r="Q57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -964,7 +964,7 @@
         <v>1.7</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
         <v>4.4</v>
@@ -982,7 +982,7 @@
         <v>2.5</v>
       </c>
       <c r="U4">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
         <v>1.33</v>
@@ -1012,7 +1012,7 @@
         <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
         <v>3</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
         <v>3.4</v>
@@ -2310,7 +2310,7 @@
         <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
         <v>1.27</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,28 +4547,28 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="P26">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T26">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
         <v>1.65</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>4.9</v>
+        <v>5.49</v>
       </c>
       <c r="AA26">
         <v>1.45</v>
       </c>
       <c r="AB26">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AC26">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD26">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG26">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="O27">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
         <v>1.65</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.49</v>
+        <v>4.9</v>
       </c>
       <c r="AA27">
         <v>1.45</v>
       </c>
       <c r="AB27">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD27">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P32">
         <v>3.6</v>
@@ -5540,16 +5540,16 @@
         <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U32">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="V32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>1.02</v>
@@ -5567,16 +5567,16 @@
         <v>2.13</v>
       </c>
       <c r="AB32">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC32">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD32">
         <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
         <v>1.92</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O36">
         <v>3.1</v>
       </c>
       <c r="P36">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>1.73</v>
+        <v>5.75</v>
       </c>
       <c r="Q37">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="R37">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T37">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="W37">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="AA37">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC37">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK37">
-        <v>1.18</v>
+        <v>2.62</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P38">
-        <v>6.15</v>
+        <v>1.26</v>
       </c>
       <c r="Q38">
-        <v>1.93</v>
+        <v>8.25</v>
       </c>
       <c r="R38">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="U38">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V38">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
         <v>1.12</v>
       </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.13</v>
-      </c>
       <c r="Z38">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD38">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.15</v>
+        <v>3.2</v>
       </c>
       <c r="AK38">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="O39">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>1.26</v>
+        <v>4.6</v>
       </c>
       <c r="Q39">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA40">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P41">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q41">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U41">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB41">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK41">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="Q42">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U42">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA42">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-07-31 15:45:00</t>
+          <t>2026-07-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q3">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -825,10 +825,10 @@
         <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.2</v>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,16 +970,16 @@
         <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
         <v>1.46</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U4">
         <v>3.2</v>
@@ -988,28 +988,28 @@
         <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.41</v>
       </c>
       <c r="Z4">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="AA4">
         <v>2.2</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
@@ -1034,7 +1034,7 @@
         <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>3.85</v>
       </c>
       <c r="P5">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="Q5">
         <v>2.2</v>
@@ -1139,7 +1139,7 @@
         <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
         <v>3.25</v>
@@ -1175,7 +1175,7 @@
         <v>1.47</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF5">
         <v>1.63</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
         <v>2.07</v>
@@ -1797,7 +1797,7 @@
         <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
         <v>1.4</v>
@@ -1830,10 +1830,10 @@
         <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
         <v>1.93</v>
@@ -1951,13 +1951,13 @@
         <v>3.12</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="U10">
         <v>2.88</v>
@@ -1978,16 +1978,16 @@
         <v>3.14</v>
       </c>
       <c r="AA10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE10">
         <v>1.04</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
         <v>1.42</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
         <v>3.4</v>
@@ -2283,16 +2283,16 @@
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
         <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,25 +2301,25 @@
         <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
         <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD12">
         <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG12">
         <v>1.93</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AK12">
         <v>1.35</v>
@@ -2431,13 +2431,13 @@
         <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
         <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="R13">
         <v>2.4</v>
@@ -2467,10 +2467,10 @@
         <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC13">
         <v>2.35</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>2.7</v>
       </c>
       <c r="Q15">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
         <v>1.28</v>
@@ -2778,13 +2778,13 @@
         <v>2.43</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.16</v>
@@ -2793,13 +2793,13 @@
         <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
         <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
         <v>1.42</v>
@@ -2811,7 +2811,7 @@
         <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>4.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="S16">
         <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
         <v>2.45</v>
@@ -2944,7 +2944,7 @@
         <v>1.49</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2953,19 +2953,19 @@
         <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AA16">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AC16">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,55 +3086,55 @@
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
         <v>2.52</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE17">
         <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG17">
         <v>2.3</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q18">
         <v>1.57</v>
@@ -3288,19 +3288,19 @@
         <v>2.49</v>
       </c>
       <c r="AC18">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AD18">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AK18">
         <v>4.33</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q22">
         <v>3.28</v>
@@ -3913,7 +3913,7 @@
         <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="U22">
         <v>3.08</v>
@@ -3934,10 +3934,10 @@
         <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AB22">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
         <v>3.68</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="R23">
         <v>2.15</v>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U23">
         <v>2.63</v>
@@ -4088,13 +4088,13 @@
         <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA23">
         <v>1.75</v>
@@ -4103,10 +4103,10 @@
         <v>2.05</v>
       </c>
       <c r="AC23">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE23">
         <v>1.09</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O24">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4245,7 +4245,7 @@
         <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4257,7 +4257,7 @@
         <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA24">
         <v>1.76</v>
@@ -4272,7 +4272,7 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>1.68</v>
       </c>
       <c r="O25">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q25">
         <v>2.1</v>
@@ -4411,7 +4411,7 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4426,7 +4426,7 @@
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
         <v>2.26</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="O26">
         <v>4.05</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S26">
         <v>1.18</v>
@@ -4595,7 +4595,7 @@
         <v>2.12</v>
       </c>
       <c r="AD26">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE26">
         <v>1.23</v>
@@ -4604,7 +4604,7 @@
         <v>1.39</v>
       </c>
       <c r="AG26">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4743,13 +4743,13 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>4.9</v>
+        <v>5.34</v>
       </c>
       <c r="AA27">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB27">
         <v>2.43</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q28">
         <v>2.28</v>
       </c>
       <c r="R28">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="U28">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.04</v>
@@ -4906,31 +4906,31 @@
         <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
+        <v>3.3</v>
+      </c>
+      <c r="AA28">
+        <v>1.96</v>
+      </c>
+      <c r="AB28">
+        <v>1.83</v>
+      </c>
+      <c r="AC28">
         <v>3.2</v>
       </c>
-      <c r="AA28">
-        <v>1.95</v>
-      </c>
-      <c r="AB28">
-        <v>1.9</v>
-      </c>
-      <c r="AC28">
-        <v>3.35</v>
-      </c>
       <c r="AD28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG28">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         <v>3.5</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -5377,25 +5377,25 @@
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
         <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
         <v>4.25</v>
@@ -5419,7 +5419,7 @@
         <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5525,25 +5525,25 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
         <v>3.05</v>
       </c>
       <c r="P32">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="R32">
         <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="U32">
         <v>3.1</v>
@@ -5552,7 +5552,7 @@
         <v>1.3</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.06</v>
@@ -5561,7 +5561,7 @@
         <v>1.39</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AA32">
         <v>2.13</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
         <v>1.7</v>
@@ -5869,7 +5869,7 @@
         <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U34">
         <v>3</v>
@@ -5890,13 +5890,13 @@
         <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB34">
         <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD34">
         <v>1.21</v>
@@ -5905,7 +5905,7 @@
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG34">
         <v>1.85</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P46">
+        <v>1.47</v>
+      </c>
+      <c r="Q46">
+        <v>5.47</v>
+      </c>
+      <c r="R46">
+        <v>2.44</v>
+      </c>
+      <c r="S46">
+        <v>1.22</v>
+      </c>
+      <c r="T46">
+        <v>3.8</v>
+      </c>
+      <c r="U46">
+        <v>2.22</v>
+      </c>
+      <c r="V46">
+        <v>1.62</v>
+      </c>
+      <c r="W46">
+        <v>1.14</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.13</v>
+      </c>
+      <c r="Z46">
+        <v>5.6</v>
+      </c>
+      <c r="AA46">
         <v>1.51</v>
       </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
-      </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>1.53</v>
-      </c>
       <c r="AB46">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC46">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD46">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL46">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R2">
         <v>2.45</v>
@@ -659,10 +659,10 @@
         <v>2.23</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,28 +671,28 @@
         <v>1.12</v>
       </c>
       <c r="Z2">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA2">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB2">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC2">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AD2">
         <v>1.55</v>
       </c>
       <c r="AE2">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG2">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1290,58 +1290,58 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q6">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R6">
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA6">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB6">
         <v>1.6</v>
       </c>
       <c r="AC6">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AG6">
         <v>1.75</v>
@@ -1622,7 +1622,7 @@
         <v>3.61</v>
       </c>
       <c r="Q8">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="R8">
         <v>2.35</v>
@@ -1631,16 +1631,16 @@
         <v>1.2</v>
       </c>
       <c r="T8">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U8">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V8">
         <v>1.66</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1652,7 +1652,7 @@
         <v>5.65</v>
       </c>
       <c r="AA8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
@@ -1661,10 +1661,10 @@
         <v>2.06</v>
       </c>
       <c r="AD8">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF8">
         <v>1.4</v>
@@ -3415,46 +3415,46 @@
         <v>4.45</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
         <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB19">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
@@ -3463,7 +3463,7 @@
         <v>1.63</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
         <v>2.1</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q20">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3596,16 +3596,16 @@
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA20">
         <v>1.41</v>
@@ -3617,10 +3617,10 @@
         <v>2.17</v>
       </c>
       <c r="AD20">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF20">
         <v>1.53</v>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>1.19</v>
       </c>
       <c r="O29">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>10.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q29">
         <v>1.48</v>
@@ -5057,7 +5057,7 @@
         <v>4</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="V29">
         <v>1.7</v>
@@ -5081,16 +5081,16 @@
         <v>2.75</v>
       </c>
       <c r="AC29">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AD29">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE29">
         <v>1.29</v>
       </c>
       <c r="AF29">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
         <v>1.85</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="O35">
         <v>3.45</v>
@@ -6023,22 +6023,22 @@
         <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="R35">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
         <v>1.32</v>
       </c>
       <c r="T35">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U35">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,28 +6050,28 @@
         <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="AA35">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC35">
         <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O37">
         <v>4.4</v>
@@ -6397,7 +6397,7 @@
         <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="O38">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q38">
         <v>8.25</v>
@@ -6518,25 +6518,25 @@
         <v>2.35</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
         <v>3.18</v>
       </c>
       <c r="U38">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
         <v>4.7</v>
@@ -6557,10 +6557,10 @@
         <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AK38">
         <v>1.01</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>4.6</v>
+        <v>2.82</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O40">
+        <v>3.3</v>
+      </c>
+      <c r="P40">
+        <v>2.32</v>
+      </c>
+      <c r="Q40">
+        <v>3.25</v>
+      </c>
+      <c r="R40">
+        <v>2.25</v>
+      </c>
+      <c r="S40">
+        <v>1.33</v>
+      </c>
+      <c r="T40">
         <v>3.2</v>
       </c>
-      <c r="P40">
-        <v>2.8</v>
-      </c>
-      <c r="Q40">
-        <v>2.98</v>
-      </c>
-      <c r="R40">
-        <v>2.19</v>
-      </c>
-      <c r="S40">
-        <v>1.38</v>
-      </c>
-      <c r="T40">
-        <v>2.7</v>
-      </c>
       <c r="U40">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AD40">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK40">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA41">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG41">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.57</v>
+      </c>
+      <c r="O42">
+        <v>3.75</v>
+      </c>
+      <c r="P42">
+        <v>5.05</v>
+      </c>
+      <c r="Q42">
+        <v>2.14</v>
+      </c>
+      <c r="R42">
         <v>2.3</v>
       </c>
-      <c r="O42">
-        <v>3.3</v>
-      </c>
-      <c r="P42">
-        <v>2.69</v>
-      </c>
-      <c r="Q42">
-        <v>2.8</v>
-      </c>
-      <c r="R42">
-        <v>2.28</v>
-      </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V42">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O44">
         <v>3.5</v>
@@ -7505,7 +7505,7 @@
         <v>2.88</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7514,7 +7514,7 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
         <v>3.18</v>
@@ -7526,19 +7526,19 @@
         <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="AD44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE44">
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,16 +7644,16 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="O45">
-        <v>5.75</v>
+        <v>6.55</v>
       </c>
       <c r="P45">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q45">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R45">
         <v>2.95</v>
@@ -7662,13 +7662,13 @@
         <v>1.15</v>
       </c>
       <c r="T45">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="U45">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V45">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W45">
         <v>1.22</v>
@@ -7677,10 +7677,10 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA45">
         <v>1.26</v>
@@ -7689,19 +7689,19 @@
         <v>3.1</v>
       </c>
       <c r="AC45">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AD45">
         <v>2</v>
       </c>
       <c r="AE45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF45">
         <v>1.61</v>
       </c>
       <c r="AG45">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O50">
-        <v>4.36</v>
+        <v>3.73</v>
       </c>
       <c r="P50">
         <v>4.5</v>
       </c>
       <c r="Q50">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8480,10 +8480,10 @@
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V50">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
         <v>1.06</v>
@@ -8492,22 +8492,22 @@
         <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
         <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.15</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="O51">
         <v>3.2</v>
@@ -8634,19 +8634,19 @@
         <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="S51">
+        <v>1.36</v>
+      </c>
+      <c r="T51">
+        <v>2.8</v>
+      </c>
+      <c r="U51">
+        <v>2.65</v>
+      </c>
+      <c r="V51">
         <v>1.4</v>
-      </c>
-      <c r="T51">
-        <v>2.75</v>
-      </c>
-      <c r="U51">
-        <v>2.8</v>
-      </c>
-      <c r="V51">
-        <v>1.36</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA51">
         <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AD51">
         <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
         <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB53">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9120,25 +9120,25 @@
         <v>2.91</v>
       </c>
       <c r="Q54">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
         <v>1.28</v>
       </c>
       <c r="T54">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U54">
         <v>2.44</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9153,22 +9153,22 @@
         <v>1.68</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC54">
         <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE54">
         <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG54">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="O56">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB56">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P57">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="Q57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>2.75</v>
@@ -816,25 +816,25 @@
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA3">
         <v>1.75</v>
@@ -843,19 +843,19 @@
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -967,19 +967,19 @@
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
         <v>3.2</v>
@@ -1012,7 +1012,7 @@
         <v>1.19</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>4.51</v>
+        <v>4.2</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R5">
         <v>2.3</v>
@@ -1172,10 +1172,10 @@
         <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.63</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="P6">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1320,22 +1320,22 @@
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z6">
         <v>2.9</v>
       </c>
       <c r="AA6">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AB6">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC6">
         <v>4.4</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
         <v>1.06</v>
@@ -1785,10 +1785,10 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S9">
         <v>1.33</v>
@@ -1797,10 +1797,10 @@
         <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
         <v>1.1</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z9">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA9">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
         <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q10">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R10">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T10">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="U10">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V10">
+        <v>1.3</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
         <v>1.33</v>
       </c>
-      <c r="W10">
-        <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.27</v>
-      </c>
       <c r="Z10">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="AA10">
         <v>2</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG10">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="R11">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG11">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.99</v>
+        <v>2.67</v>
       </c>
       <c r="O12">
         <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q12">
         <v>3.4</v>
@@ -2289,7 +2289,7 @@
         <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2313,16 +2313,16 @@
         <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.52</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>1.25</v>
@@ -2455,7 +2455,7 @@
         <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2467,10 +2467,10 @@
         <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC13">
         <v>2.35</v>
@@ -2482,7 +2482,7 @@
         <v>1.19</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2594,7 +2594,7 @@
         <v>3.4</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
         <v>1.91</v>
@@ -2766,7 +2766,7 @@
         <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.28</v>
@@ -2775,7 +2775,7 @@
         <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="V15">
         <v>1.5</v>
@@ -2784,10 +2784,10 @@
         <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
         <v>4.2</v>
@@ -2799,7 +2799,7 @@
         <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
         <v>1.42</v>
@@ -2917,55 +2917,55 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
       </c>
       <c r="R16">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
         <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AA16">
         <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
@@ -2974,7 +2974,7 @@
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3086,13 +3086,13 @@
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
         <v>1.3</v>
@@ -3104,10 +3104,10 @@
         <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.02</v>
@@ -3116,13 +3116,13 @@
         <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
         <v>2.52</v>
@@ -3134,7 +3134,7 @@
         <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
         <v>2.3</v>
@@ -3153,7 +3153,7 @@
         <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>1.2</v>
       </c>
       <c r="O18">
-        <v>5.75</v>
+        <v>6.55</v>
       </c>
       <c r="P18">
-        <v>9.5</v>
+        <v>12.3</v>
       </c>
       <c r="Q18">
         <v>1.57</v>
@@ -3273,7 +3273,7 @@
         <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.13</v>
@@ -3291,16 +3291,16 @@
         <v>2.29</v>
       </c>
       <c r="AD18">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
         <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
         <v>4.33</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="O22">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q22">
         <v>3.28</v>
@@ -3913,7 +3913,7 @@
         <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="U22">
         <v>3.08</v>
@@ -3934,13 +3934,13 @@
         <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
         <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="AD22">
         <v>1.27</v>
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q23">
-        <v>3.51</v>
+        <v>3.13</v>
       </c>
       <c r="R23">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
+        <v>1.35</v>
+      </c>
+      <c r="T23">
+        <v>2.88</v>
+      </c>
+      <c r="U23">
+        <v>2.71</v>
+      </c>
+      <c r="V23">
+        <v>1.37</v>
+      </c>
+      <c r="W23">
+        <v>1.04</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>3.42</v>
+      </c>
+      <c r="AA23">
+        <v>1.8</v>
+      </c>
+      <c r="AB23">
+        <v>2</v>
+      </c>
+      <c r="AC23">
+        <v>3.08</v>
+      </c>
+      <c r="AD23">
+        <v>1.28</v>
+      </c>
+      <c r="AE23">
+        <v>1.06</v>
+      </c>
+      <c r="AF23">
+        <v>1.6</v>
+      </c>
+      <c r="AG23">
+        <v>2.05</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.25</v>
+      </c>
+      <c r="AK23">
         <v>1.3</v>
-      </c>
-      <c r="T23">
-        <v>3.04</v>
-      </c>
-      <c r="U23">
-        <v>2.63</v>
-      </c>
-      <c r="V23">
-        <v>1.44</v>
-      </c>
-      <c r="W23">
-        <v>1.06</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.18</v>
-      </c>
-      <c r="Z23">
-        <v>3.84</v>
-      </c>
-      <c r="AA23">
-        <v>1.75</v>
-      </c>
-      <c r="AB23">
-        <v>2.05</v>
-      </c>
-      <c r="AC23">
-        <v>2.78</v>
-      </c>
-      <c r="AD23">
-        <v>1.34</v>
-      </c>
-      <c r="AE23">
-        <v>1.09</v>
-      </c>
-      <c r="AF23">
-        <v>1.58</v>
-      </c>
-      <c r="AG23">
-        <v>2.19</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.53</v>
-      </c>
-      <c r="AK23">
-        <v>1.34</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P24">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
       </c>
       <c r="R24">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4257,7 +4257,7 @@
         <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA24">
         <v>1.76</v>
@@ -4272,7 +4272,7 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -4387,7 +4387,7 @@
         <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P25">
         <v>4</v>
@@ -4411,7 +4411,7 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.02</v>
@@ -4426,7 +4426,7 @@
         <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="AC25">
         <v>2.26</v>
@@ -4435,7 +4435,7 @@
         <v>1.61</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF25">
         <v>1.48</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="O26">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
@@ -4562,7 +4562,7 @@
         <v>2.46</v>
       </c>
       <c r="S26">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T26">
         <v>3.86</v>
@@ -4577,10 +4577,10 @@
         <v>1.14</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
         <v>5.49</v>
@@ -4589,7 +4589,7 @@
         <v>1.45</v>
       </c>
       <c r="AB26">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AC26">
         <v>2.12</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="Q27">
         <v>2.65</v>
@@ -4746,19 +4746,19 @@
         <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>5.34</v>
+        <v>5.4</v>
       </c>
       <c r="AA27">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AC27">
         <v>2.16</v>
       </c>
       <c r="AD27">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE27">
         <v>1.22</v>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
         <v>2.74</v>
@@ -4897,7 +4897,7 @@
         <v>2.78</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
         <v>1.04</v>
@@ -4924,7 +4924,7 @@
         <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
         <v>1.8</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="O29">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P29">
-        <v>9.75</v>
+        <v>11.5</v>
       </c>
       <c r="Q29">
         <v>1.48</v>
@@ -5057,13 +5057,13 @@
         <v>4</v>
       </c>
       <c r="U29">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V29">
         <v>1.7</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,22 +5072,22 @@
         <v>1.07</v>
       </c>
       <c r="Z29">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA29">
         <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC29">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AD29">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AE29">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF29">
         <v>1.83</v>
@@ -5109,7 +5109,7 @@
         <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,22 +5362,22 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
         <v>3.7</v>
       </c>
       <c r="P31">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q31">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
         <v>3.25</v>
@@ -5389,22 +5389,22 @@
         <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>4.53</v>
       </c>
       <c r="AA31">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC31">
         <v>2.46</v>
@@ -5419,7 +5419,7 @@
         <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
         <v>1.7</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="O34">
         <v>3.1</v>
@@ -5875,7 +5875,7 @@
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5896,16 +5896,16 @@
         <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD34">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
         <v>1.85</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="O35">
         <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
@@ -6035,10 +6035,10 @@
         <v>3.05</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6047,7 +6047,7 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
         <v>4.23</v>
@@ -6056,7 +6056,7 @@
         <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AC35">
         <v>2.59</v>
@@ -6183,7 +6183,7 @@
         <v>3.1</v>
       </c>
       <c r="P36">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -7810,52 +7810,52 @@
         <v>5.34</v>
       </c>
       <c r="O46">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P46">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="Q46">
-        <v>5.47</v>
+        <v>4.9</v>
       </c>
       <c r="R46">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U46">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
         <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
         <v>5.6</v>
       </c>
       <c r="AA46">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AB46">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="AC46">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE46">
         <v>1.26</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -9123,22 +9123,22 @@
         <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S54">
         <v>1.28</v>
       </c>
       <c r="T54">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W54">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.04</v>
@@ -9153,7 +9153,7 @@
         <v>1.68</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC54">
         <v>2.7</v>
@@ -9165,7 +9165,7 @@
         <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG54">
         <v>2.3</v>
@@ -9184,7 +9184,7 @@
         <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O56">
         <v>3.4</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q2">
         <v>2.31</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
         <v>5</v>
@@ -677,22 +677,22 @@
         <v>1.53</v>
       </c>
       <c r="AB2">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC2">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
         <v>1.55</v>
       </c>
       <c r="AE2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF2">
         <v>1.48</v>
       </c>
       <c r="AG2">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
         <v>3.74</v>
@@ -1622,7 +1622,7 @@
         <v>3.61</v>
       </c>
       <c r="Q8">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R8">
         <v>2.35</v>
@@ -1634,25 +1634,25 @@
         <v>3.68</v>
       </c>
       <c r="U8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
         <v>1.66</v>
       </c>
       <c r="W8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
         <v>5.65</v>
       </c>
       <c r="AA8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
@@ -1670,7 +1670,7 @@
         <v>1.4</v>
       </c>
       <c r="AG8">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R19">
         <v>2.3</v>
@@ -3424,10 +3424,10 @@
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
         <v>1.5</v>
@@ -3436,25 +3436,25 @@
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="AA19">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
         <v>2.1</v>
@@ -3572,10 +3572,10 @@
         <v>1.58</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="Q20">
         <v>2</v>
@@ -3596,10 +3596,10 @@
         <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.08</v>
@@ -3611,7 +3611,7 @@
         <v>1.41</v>
       </c>
       <c r="AB20">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC20">
         <v>2.17</v>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
         <v>4.4</v>
       </c>
       <c r="P37">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>1.93</v>
@@ -6367,7 +6367,7 @@
         <v>1.59</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,7 +6376,7 @@
         <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="AA37">
         <v>1.53</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK37">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P38">
         <v>1.28</v>
@@ -6515,7 +6515,7 @@
         <v>8.25</v>
       </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="S38">
         <v>1.22</v>
@@ -6530,19 +6530,19 @@
         <v>1.65</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
         <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>4.7</v>
+        <v>4.99</v>
       </c>
       <c r="AA38">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
         <v>2.28</v>
@@ -6554,14 +6554,14 @@
         <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
+        <v>1.75</v>
+      </c>
+      <c r="AG38">
         <v>1.83</v>
       </c>
-      <c r="AG38">
-        <v>1.86</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AK38">
         <v>1.01</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="Q39">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
         <v>2.19</v>
@@ -6687,10 +6687,10 @@
         <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6702,7 +6702,7 @@
         <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
         <v>1.95</v>
@@ -6711,19 +6711,19 @@
         <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
         <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>2.04</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S40">
         <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="Q41">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U41">
         <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>5.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
+        <v>2.13</v>
+      </c>
+      <c r="S42">
+        <v>1.3</v>
+      </c>
+      <c r="T42">
+        <v>3.08</v>
+      </c>
+      <c r="U42">
+        <v>2.41</v>
+      </c>
+      <c r="V42">
+        <v>1.48</v>
+      </c>
+      <c r="W42">
+        <v>1.12</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.16</v>
+      </c>
+      <c r="Z42">
+        <v>4.15</v>
+      </c>
+      <c r="AA42">
+        <v>1.66</v>
+      </c>
+      <c r="AB42">
+        <v>2.12</v>
+      </c>
+      <c r="AC42">
+        <v>2.65</v>
+      </c>
+      <c r="AD42">
+        <v>1.48</v>
+      </c>
+      <c r="AE42">
+        <v>1.18</v>
+      </c>
+      <c r="AF42">
+        <v>1.55</v>
+      </c>
+      <c r="AG42">
         <v>2.3</v>
       </c>
-      <c r="S42">
-        <v>1.31</v>
-      </c>
-      <c r="T42">
-        <v>3.26</v>
-      </c>
-      <c r="U42">
-        <v>2.6</v>
-      </c>
-      <c r="V42">
-        <v>1.46</v>
-      </c>
-      <c r="W42">
-        <v>1.1</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.18</v>
-      </c>
-      <c r="Z42">
-        <v>4</v>
-      </c>
-      <c r="AA42">
-        <v>1.72</v>
-      </c>
-      <c r="AB42">
-        <v>2</v>
-      </c>
-      <c r="AC42">
-        <v>2.48</v>
-      </c>
-      <c r="AD42">
-        <v>1.36</v>
-      </c>
-      <c r="AE42">
-        <v>1.1</v>
-      </c>
-      <c r="AF42">
-        <v>1.75</v>
-      </c>
-      <c r="AG42">
-        <v>1.95</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q44">
         <v>4.75</v>
@@ -7505,7 +7505,7 @@
         <v>2.88</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7517,7 +7517,7 @@
         <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="AA44">
         <v>2</v>
@@ -7535,10 +7535,10 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7647,28 +7647,28 @@
         <v>1.21</v>
       </c>
       <c r="O45">
-        <v>6.55</v>
+        <v>5.75</v>
       </c>
       <c r="P45">
         <v>8</v>
       </c>
       <c r="Q45">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R45">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="S45">
         <v>1.15</v>
       </c>
       <c r="T45">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="U45">
         <v>1.83</v>
       </c>
       <c r="V45">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W45">
         <v>1.22</v>
@@ -7677,28 +7677,28 @@
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="AA45">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AB45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC45">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD45">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AE45">
         <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
         <v>2.15</v>
@@ -7717,7 +7717,7 @@
         <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>1.62</v>
       </c>
       <c r="O50">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
         <v>4.5</v>
@@ -8480,7 +8480,7 @@
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V50">
         <v>1.45</v>
@@ -8489,10 +8489,10 @@
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
         <v>4.1</v>
@@ -8501,7 +8501,7 @@
         <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
         <v>2.8</v>
@@ -8510,7 +8510,7 @@
         <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
         <v>1.68</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -8646,10 +8646,10 @@
         <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8661,7 +8661,7 @@
         <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB51">
         <v>1.86</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK51">
         <v>1.44</v>
@@ -9147,7 +9147,7 @@
         <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AA54">
         <v>1.68</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O56">
         <v>3.4</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9603,10 +9603,10 @@
         <v>2.49</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -6340,40 +6340,40 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P37">
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R37">
         <v>2.55</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
         <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
         <v>4.4</v>
@@ -6388,16 +6388,16 @@
         <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q40">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
         <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -6856,37 +6856,37 @@
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AK40">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>2.04</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U42">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="AD42">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK42">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q44">
         <v>4.75</v>
@@ -7810,10 +7810,10 @@
         <v>5.34</v>
       </c>
       <c r="O46">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q46">
         <v>4.9</v>
@@ -7843,22 +7843,22 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB46">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
         <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AE46">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
         <v>1.6</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="P50">
         <v>4.5</v>
@@ -8471,7 +8471,7 @@
         <v>2.13</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.29</v>
@@ -8492,7 +8492,7 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
         <v>4.1</v>
@@ -8501,7 +8501,7 @@
         <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
         <v>2.8</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R2">
         <v>2.45</v>
@@ -662,7 +662,7 @@
         <v>1.62</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -671,13 +671,13 @@
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="AA2">
         <v>1.53</v>
       </c>
       <c r="AB2">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC2">
         <v>2.25</v>
@@ -686,7 +686,7 @@
         <v>1.55</v>
       </c>
       <c r="AE2">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
         <v>1.48</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="Q3">
         <v>2.75</v>
@@ -834,7 +834,7 @@
         <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA3">
         <v>1.75</v>
@@ -843,16 +843,16 @@
         <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
         <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
         <v>2.15</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="Q4">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T4">
         <v>2.5</v>
       </c>
       <c r="U4">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1.03</v>
@@ -1012,7 +1012,7 @@
         <v>1.19</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
       <c r="Q5">
         <v>2.15</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="O6">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="P6">
         <v>2.3</v>
@@ -1302,10 +1302,10 @@
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="U6">
         <v>3.1</v>
@@ -1320,25 +1320,25 @@
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA6">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AC6">
         <v>4.4</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
         <v>1.89</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P7">
-        <v>6.76</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA7">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
         <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG7">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>3.74</v>
+        <v>3.66</v>
       </c>
       <c r="P8">
-        <v>3.61</v>
+        <v>3.29</v>
       </c>
       <c r="Q8">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="R8">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T8">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U8">
         <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W8">
         <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.1</v>
       </c>
       <c r="Z8">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
       </c>
       <c r="AC8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AD8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE8">
         <v>1.24</v>
       </c>
       <c r="AF8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG8">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q9">
         <v>2.21</v>
@@ -1797,13 +1797,13 @@
         <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
         <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1818,13 +1818,13 @@
         <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
         <v>1.09</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="Q10">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="R10">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
         <v>3.04</v>
@@ -1969,13 +1969,13 @@
         <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AA10">
         <v>2</v>
@@ -1984,19 +1984,19 @@
         <v>1.78</v>
       </c>
       <c r="AC10">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,19 +2102,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q11">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2135,13 +2135,13 @@
         <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
         <v>1.8</v>
@@ -2153,7 +2153,7 @@
         <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
         <v>1.74</v>
@@ -2175,7 +2175,7 @@
         <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="P12">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
         <v>3.4</v>
@@ -2286,10 +2286,10 @@
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2313,16 +2313,16 @@
         <v>3.14</v>
       </c>
       <c r="AD12">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG12">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.52</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
         <v>1.75</v>
@@ -2455,7 +2455,7 @@
         <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,25 +2464,25 @@
         <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>4.97</v>
       </c>
       <c r="AA13">
         <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC13">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2594,7 +2594,7 @@
         <v>3.4</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P14">
         <v>1.91</v>
@@ -2760,19 +2760,19 @@
         <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q15">
         <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
         <v>2.35</v>
@@ -2784,10 +2784,10 @@
         <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
         <v>4.2</v>
@@ -2799,7 +2799,7 @@
         <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
         <v>1.42</v>
@@ -2811,7 +2811,7 @@
         <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O16">
         <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -2941,13 +2941,13 @@
         <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.22</v>
@@ -2959,7 +2959,7 @@
         <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
         <v>2.75</v>
@@ -2971,10 +2971,10 @@
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.6</v>
@@ -3086,7 +3086,7 @@
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
@@ -3098,7 +3098,7 @@
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="U17">
         <v>2.38</v>
@@ -3122,7 +3122,7 @@
         <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC17">
         <v>2.52</v>
@@ -3131,7 +3131,7 @@
         <v>1.41</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.55</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,34 +3246,34 @@
         <v>1.2</v>
       </c>
       <c r="O18">
-        <v>6.55</v>
+        <v>6.7</v>
       </c>
       <c r="P18">
-        <v>12.3</v>
+        <v>13.2</v>
       </c>
       <c r="Q18">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R18">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
         <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.13</v>
@@ -3282,25 +3282,25 @@
         <v>5.4</v>
       </c>
       <c r="AA18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB18">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AC18">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
         <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.08</v>
       </c>
       <c r="AK18">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="P22">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
         <v>3.28</v>
@@ -3934,13 +3934,13 @@
         <v>3.1</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB22">
         <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="AD22">
         <v>1.27</v>
@@ -4058,43 +4058,43 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.13</v>
+        <v>3.59</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U23">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
         <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
         <v>1.8</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK23">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="O24">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q24">
         <v>2.19</v>
@@ -4257,7 +4257,7 @@
         <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA24">
         <v>1.76</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
         <v>2.15</v>
@@ -4390,7 +4390,7 @@
         <v>4.05</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q25">
         <v>2.1</v>
@@ -4423,25 +4423,25 @@
         <v>4.95</v>
       </c>
       <c r="AA25">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AC25">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AD25">
         <v>1.61</v>
       </c>
       <c r="AE25">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG25">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="P26">
         <v>2.4</v>
@@ -4559,37 +4559,37 @@
         <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="S26">
         <v>1.22</v>
       </c>
       <c r="T26">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="U26">
         <v>2.1</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W26">
         <v>1.14</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
-        <v>5.49</v>
+        <v>5.57</v>
       </c>
       <c r="AA26">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AC26">
         <v>2.12</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,13 +4713,13 @@
         <v>2.15</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="Q27">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R27">
         <v>2.31</v>
@@ -4731,7 +4731,7 @@
         <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
         <v>1.62</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
         <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
         <v>2.16</v>
       </c>
       <c r="AD27">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF27">
         <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,19 +4876,19 @@
         <v>1.73</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R28">
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
         <v>2.74</v>
@@ -4897,7 +4897,7 @@
         <v>2.78</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.04</v>
@@ -4912,16 +4912,16 @@
         <v>3.3</v>
       </c>
       <c r="AA28">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC28">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.08</v>
@@ -5042,10 +5042,10 @@
         <v>6.6</v>
       </c>
       <c r="P29">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q29">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R29">
         <v>3</v>
@@ -5084,16 +5084,16 @@
         <v>1.98</v>
       </c>
       <c r="AD29">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AE29">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF29">
         <v>1.83</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5365,49 +5365,49 @@
         <v>3.25</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
         <v>3.6</v>
       </c>
       <c r="R31">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>4.53</v>
+        <v>4.25</v>
       </c>
       <c r="AA31">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AD31">
         <v>1.48</v>
@@ -5419,7 +5419,7 @@
         <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.75</v>
       </c>
       <c r="AK31">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O32">
         <v>3.05</v>
@@ -5534,7 +5534,7 @@
         <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="R32">
         <v>2.05</v>
@@ -5561,7 +5561,7 @@
         <v>1.39</v>
       </c>
       <c r="Z32">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AA32">
         <v>2.13</v>
@@ -5598,7 +5598,7 @@
         <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U33">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V33">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
         <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="O34">
         <v>3.1</v>
@@ -5869,13 +5869,13 @@
         <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U34">
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5884,7 +5884,7 @@
         <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
         <v>2.97</v>
@@ -5896,16 +5896,16 @@
         <v>1.7</v>
       </c>
       <c r="AC34">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG34">
         <v>1.85</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="P35">
         <v>2.14</v>
@@ -6032,13 +6032,13 @@
         <v>1.32</v>
       </c>
       <c r="T35">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="U35">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6050,7 +6050,7 @@
         <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
         <v>1.67</v>
@@ -6062,7 +6062,7 @@
         <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE35">
         <v>1.15</v>
@@ -6180,10 +6180,10 @@
         <v>3.25</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P36">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>1.28</v>
@@ -6515,31 +6515,31 @@
         <v>8.25</v>
       </c>
       <c r="R38">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="S38">
         <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U38">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V38">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
         <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="AA38">
         <v>1.53</v>
@@ -6548,7 +6548,7 @@
         <v>2.28</v>
       </c>
       <c r="AC38">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD38">
         <v>1.43</v>
@@ -6560,7 +6560,7 @@
         <v>1.75</v>
       </c>
       <c r="AG38">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AK38">
         <v>1.01</v>
@@ -6672,7 +6672,7 @@
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="Q39">
         <v>3.05</v>
@@ -6687,10 +6687,10 @@
         <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6702,7 +6702,7 @@
         <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
         <v>1.95</v>
@@ -6714,7 +6714,7 @@
         <v>3.14</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE39">
         <v>1.1</v>
@@ -6723,7 +6723,7 @@
         <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AD41">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="R42">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
         <v>1.33</v>
       </c>
       <c r="T42">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V42">
         <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z42">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AK42">
-        <v>2.25</v>
+        <v>1.34</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,37 +7807,37 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.34</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P46">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Q46">
         <v>4.9</v>
       </c>
       <c r="R46">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="U46">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V46">
         <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
@@ -7846,7 +7846,7 @@
         <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
         <v>2.5</v>
@@ -7855,13 +7855,13 @@
         <v>2.25</v>
       </c>
       <c r="AD46">
+        <v>1.62</v>
+      </c>
+      <c r="AE46">
+        <v>1.22</v>
+      </c>
+      <c r="AF46">
         <v>1.57</v>
-      </c>
-      <c r="AE46">
-        <v>1.25</v>
-      </c>
-      <c r="AF46">
-        <v>1.6</v>
       </c>
       <c r="AG46">
         <v>2.25</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
         <v>1.14</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
         <v>2.38</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AA53">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -3406,46 +3406,46 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
         <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="AA19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
@@ -3454,7 +3454,7 @@
         <v>2.62</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P20">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
         <v>2</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3599,28 +3599,28 @@
         <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AD20">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE20">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF20">
         <v>1.53</v>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -6376,7 +6376,7 @@
         <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AA37">
         <v>1.53</v>
@@ -6388,10 +6388,10 @@
         <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF37">
         <v>1.69</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.7</v>
+      </c>
+      <c r="O40">
+        <v>3.35</v>
+      </c>
+      <c r="P40">
+        <v>2.16</v>
+      </c>
+      <c r="Q40">
+        <v>3.25</v>
+      </c>
+      <c r="R40">
         <v>2.25</v>
       </c>
-      <c r="O40">
-        <v>3.4</v>
-      </c>
-      <c r="P40">
-        <v>2.6</v>
-      </c>
-      <c r="Q40">
-        <v>2.88</v>
-      </c>
-      <c r="R40">
-        <v>2.13</v>
-      </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="U40">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V40">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC40">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AD40">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK40">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC41">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,37 +7155,37 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U42">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V42">
         <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.19</v>
@@ -7194,25 +7194,25 @@
         <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG42">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AK42">
-        <v>1.34</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7487,7 +7487,7 @@
         <v>3.5</v>
       </c>
       <c r="P44">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q44">
         <v>4.75</v>
@@ -7496,7 +7496,7 @@
         <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
         <v>2.9</v>
@@ -7508,7 +7508,7 @@
         <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,7 +7517,7 @@
         <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA44">
         <v>2</v>
@@ -7526,19 +7526,19 @@
         <v>1.75</v>
       </c>
       <c r="AC44">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="AD44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="O45">
-        <v>5.75</v>
+        <v>6.65</v>
       </c>
       <c r="P45">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="Q45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R45">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="S45">
         <v>1.15</v>
       </c>
       <c r="T45">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U45">
         <v>1.83</v>
@@ -7683,7 +7683,7 @@
         <v>6.4</v>
       </c>
       <c r="AA45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB45">
         <v>3.2</v>
@@ -7692,16 +7692,16 @@
         <v>1.73</v>
       </c>
       <c r="AD45">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AE45">
         <v>1.4</v>
       </c>
       <c r="AF45">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG45">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8462,16 +8462,16 @@
         <v>1.61</v>
       </c>
       <c r="O50">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q50">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S50">
         <v>1.29</v>
@@ -8480,13 +8480,13 @@
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="V50">
         <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8495,19 +8495,19 @@
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
         <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
         <v>1.1</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P51">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="S51">
         <v>1.36</v>
@@ -8643,16 +8643,16 @@
         <v>2.8</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.26</v>
@@ -8661,22 +8661,22 @@
         <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
         <v>2.95</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
         <v>1.95</v>
@@ -9111,37 +9111,37 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="O54">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="P54">
-        <v>2.91</v>
+        <v>3.65</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="R54">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="S54">
         <v>1.28</v>
       </c>
       <c r="T54">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U54">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="V54">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W54">
         <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.17</v>
@@ -9150,13 +9150,13 @@
         <v>4</v>
       </c>
       <c r="AA54">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB54">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD54">
         <v>1.36</v>
@@ -9165,7 +9165,7 @@
         <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
         <v>2.3</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,10 +9283,10 @@
         <v>4.11</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9328,10 +9328,10 @@
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P56">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA56">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB56">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U41">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AD41">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
-        <v>1.49</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R42">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U42">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.46</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC42">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD42">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
         <v>3.27</v>
@@ -3931,19 +3931,19 @@
         <v>1.32</v>
       </c>
       <c r="Z22">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AA22">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB22">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC22">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
         <v>1.03</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,37 +6829,37 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="O40">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U40">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V40">
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
         <v>1.19</v>
@@ -6868,25 +6868,25 @@
         <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC40">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>1.34</v>
+        <v>2.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,37 +6992,37 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V41">
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y41">
         <v>1.19</v>
@@ -7031,25 +7031,25 @@
         <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>1.34</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="O54">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q54">
         <v>2.25</v>
       </c>
       <c r="R54">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S54">
+        <v>1.3</v>
+      </c>
+      <c r="T54">
+        <v>3.1</v>
+      </c>
+      <c r="U54">
+        <v>2.7</v>
+      </c>
+      <c r="V54">
+        <v>1.48</v>
+      </c>
+      <c r="W54">
+        <v>1.07</v>
+      </c>
+      <c r="X54">
+        <v>1.02</v>
+      </c>
+      <c r="Y54">
+        <v>1.23</v>
+      </c>
+      <c r="Z54">
+        <v>3.42</v>
+      </c>
+      <c r="AA54">
+        <v>1.71</v>
+      </c>
+      <c r="AB54">
+        <v>1.88</v>
+      </c>
+      <c r="AC54">
+        <v>3.08</v>
+      </c>
+      <c r="AD54">
         <v>1.28</v>
       </c>
-      <c r="T54">
-        <v>3.12</v>
-      </c>
-      <c r="U54">
-        <v>2.44</v>
-      </c>
-      <c r="V54">
-        <v>1.53</v>
-      </c>
-      <c r="W54">
-        <v>1.08</v>
-      </c>
-      <c r="X54">
-        <v>1.03</v>
-      </c>
-      <c r="Y54">
-        <v>1.17</v>
-      </c>
-      <c r="Z54">
-        <v>4</v>
-      </c>
-      <c r="AA54">
+      <c r="AE54">
+        <v>1.05</v>
+      </c>
+      <c r="AF54">
         <v>1.67</v>
       </c>
-      <c r="AB54">
-        <v>2.1</v>
-      </c>
-      <c r="AC54">
-        <v>2.69</v>
-      </c>
-      <c r="AD54">
-        <v>1.36</v>
-      </c>
-      <c r="AE54">
-        <v>1.1</v>
-      </c>
-      <c r="AF54">
-        <v>1.65</v>
-      </c>
       <c r="AG54">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O56">
         <v>3.28</v>
       </c>
       <c r="P56">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="Q56">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R56">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T56">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V56">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
         <v>1.06</v>
@@ -9470,22 +9470,22 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB56">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC56">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AD56">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE56">
         <v>1.07</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O2">
+        <v>3.9</v>
+      </c>
+      <c r="P2">
         <v>3.6</v>
       </c>
-      <c r="P2">
-        <v>3.15</v>
-      </c>
       <c r="Q2">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="R2">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="U2">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="V2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W2">
         <v>1.12</v>
@@ -668,31 +668,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>4.94</v>
+        <v>5.01</v>
       </c>
       <c r="AA2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB2">
         <v>2.4</v>
       </c>
       <c r="AC2">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AD2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="Q3">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>2.2</v>
@@ -819,43 +819,43 @@
         <v>2.92</v>
       </c>
       <c r="U3">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC3">
         <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
         <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P4">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="Q4">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U4">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -991,34 +991,34 @@
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
         <v>1.41</v>
       </c>
       <c r="Z4">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD4">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>4.51</v>
+        <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T5">
         <v>3.25</v>
@@ -1181,7 +1181,7 @@
         <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
         <v>2.07</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="O6">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q6">
         <v>3.8</v>
@@ -1302,43 +1302,43 @@
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.27</v>
+        <v>2.64</v>
       </c>
       <c r="U6">
         <v>3.1</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z6">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="AA6">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AB6">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC6">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
         <v>1.89</v>
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O8">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>3.29</v>
+        <v>3.46</v>
       </c>
       <c r="Q8">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="R8">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U8">
         <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
       </c>
       <c r="AC8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE8">
         <v>1.24</v>
@@ -1670,7 +1670,7 @@
         <v>1.39</v>
       </c>
       <c r="AG8">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="Q9">
-        <v>2.21</v>
+        <v>3.04</v>
       </c>
       <c r="R9">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="S9">
+        <v>1.36</v>
+      </c>
+      <c r="T9">
+        <v>2.8</v>
+      </c>
+      <c r="U9">
+        <v>3.05</v>
+      </c>
+      <c r="V9">
+        <v>1.3</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
         <v>1.33</v>
       </c>
-      <c r="T9">
-        <v>2.88</v>
-      </c>
-      <c r="U9">
-        <v>2.56</v>
-      </c>
-      <c r="V9">
-        <v>1.41</v>
-      </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
+      <c r="Z9">
+        <v>2.92</v>
+      </c>
+      <c r="AA9">
+        <v>2.05</v>
+      </c>
+      <c r="AB9">
+        <v>1.67</v>
+      </c>
+      <c r="AC9">
+        <v>3.58</v>
+      </c>
+      <c r="AD9">
         <v>1.25</v>
       </c>
-      <c r="Z9">
-        <v>3.5</v>
-      </c>
-      <c r="AA9">
-        <v>1.78</v>
-      </c>
-      <c r="AB9">
-        <v>1.95</v>
-      </c>
-      <c r="AC9">
-        <v>2.88</v>
-      </c>
-      <c r="AD9">
-        <v>1.33</v>
-      </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
         <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.99</v>
+        <v>2.37</v>
       </c>
       <c r="Q10">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="R10">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
         <v>2.88</v>
       </c>
       <c r="U10">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="V10">
+        <v>1.33</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
         <v>1.3</v>
       </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.31</v>
-      </c>
       <c r="Z10">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC10">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD10">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
         <v>2</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AK10">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>3.02</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
+        <v>1.41</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.25</v>
+      </c>
+      <c r="Z11">
+        <v>3.5</v>
+      </c>
+      <c r="AA11">
+        <v>1.78</v>
+      </c>
+      <c r="AB11">
+        <v>1.91</v>
+      </c>
+      <c r="AC11">
+        <v>3.1</v>
+      </c>
+      <c r="AD11">
         <v>1.33</v>
       </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.28</v>
-      </c>
-      <c r="Z11">
-        <v>3.08</v>
-      </c>
-      <c r="AA11">
-        <v>1.98</v>
-      </c>
-      <c r="AB11">
-        <v>1.8</v>
-      </c>
-      <c r="AC11">
-        <v>3.4</v>
-      </c>
-      <c r="AD11">
-        <v>1.3</v>
-      </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="O12">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q12">
         <v>3.4</v>
@@ -2280,49 +2280,49 @@
         <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.29</v>
       </c>
       <c r="Z12">
+        <v>3.15</v>
+      </c>
+      <c r="AA12">
+        <v>1.94</v>
+      </c>
+      <c r="AB12">
+        <v>1.85</v>
+      </c>
+      <c r="AC12">
         <v>3.4</v>
       </c>
-      <c r="AA12">
-        <v>1.95</v>
-      </c>
-      <c r="AB12">
-        <v>1.74</v>
-      </c>
-      <c r="AC12">
-        <v>3.14</v>
-      </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AK12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>1.91</v>
+        <v>2.95</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA14">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB14">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R15">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
+        <v>2.12</v>
+      </c>
+      <c r="O16">
+        <v>3.52</v>
+      </c>
+      <c r="P16">
+        <v>3.15</v>
+      </c>
+      <c r="Q16">
+        <v>2.7</v>
+      </c>
+      <c r="R16">
+        <v>2.19</v>
+      </c>
+      <c r="S16">
+        <v>1.29</v>
+      </c>
+      <c r="T16">
+        <v>3.1</v>
+      </c>
+      <c r="U16">
+        <v>2.31</v>
+      </c>
+      <c r="V16">
+        <v>1.52</v>
+      </c>
+      <c r="W16">
+        <v>1.13</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.16</v>
+      </c>
+      <c r="Z16">
+        <v>4.05</v>
+      </c>
+      <c r="AA16">
+        <v>1.66</v>
+      </c>
+      <c r="AB16">
+        <v>2.15</v>
+      </c>
+      <c r="AC16">
+        <v>2.52</v>
+      </c>
+      <c r="AD16">
+        <v>1.41</v>
+      </c>
+      <c r="AE16">
+        <v>1.13</v>
+      </c>
+      <c r="AF16">
+        <v>1.55</v>
+      </c>
+      <c r="AG16">
         <v>2.3</v>
       </c>
-      <c r="O16">
-        <v>3.4</v>
-      </c>
-      <c r="P16">
-        <v>2.7</v>
-      </c>
-      <c r="Q16">
-        <v>2.75</v>
-      </c>
-      <c r="R16">
-        <v>2.25</v>
-      </c>
-      <c r="S16">
-        <v>1.28</v>
-      </c>
-      <c r="T16">
-        <v>3.25</v>
-      </c>
-      <c r="U16">
-        <v>2.45</v>
-      </c>
-      <c r="V16">
-        <v>1.5</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.22</v>
       </c>
-      <c r="Z16">
-        <v>3.94</v>
-      </c>
-      <c r="AA16">
-        <v>1.7</v>
-      </c>
-      <c r="AB16">
-        <v>2.1</v>
-      </c>
-      <c r="AC16">
-        <v>2.75</v>
-      </c>
-      <c r="AD16">
-        <v>1.4</v>
-      </c>
-      <c r="AE16">
-        <v>1.11</v>
-      </c>
-      <c r="AF16">
-        <v>1.56</v>
-      </c>
-      <c r="AG16">
-        <v>2.28</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.25</v>
-      </c>
       <c r="AK16">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>3.89</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
+        <v>4</v>
+      </c>
+      <c r="R17">
         <v>2.5</v>
       </c>
-      <c r="R17">
-        <v>2.19</v>
-      </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U17">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB17">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC17">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AD17">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O18">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
       <c r="Q18">
         <v>1.55</v>
       </c>
       <c r="R18">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.13</v>
@@ -3282,25 +3282,25 @@
         <v>5.4</v>
       </c>
       <c r="AA18">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG18">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>1.96</v>
       </c>
       <c r="S22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T22">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>3.08</v>
@@ -3928,13 +3928,13 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
         <v>3.26</v>
       </c>
       <c r="AA22">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB22">
         <v>1.8</v>
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG22">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,52 +4058,52 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
         <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T23">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
         <v>1.04</v>
       </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD23">
         <v>1.29</v>
@@ -4112,10 +4112,10 @@
         <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="Q24">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4245,7 +4245,7 @@
         <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4254,16 +4254,16 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
         <v>3.95</v>
       </c>
       <c r="AA24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC24">
         <v>2.85</v>
@@ -4272,13 +4272,13 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
         <v>2.15</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="O25">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q25">
         <v>2.1</v>
@@ -4411,13 +4411,13 @@
         <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
         <v>4.95</v>
@@ -4426,22 +4426,22 @@
         <v>1.51</v>
       </c>
       <c r="AB25">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC25">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AD25">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE25">
         <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG25">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="O26">
-        <v>3.84</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="R26">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T26">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>5.57</v>
+        <v>4.9</v>
       </c>
       <c r="AA26">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AC26">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD26">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE26">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF26">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
         <v>1.2</v>
       </c>
       <c r="T27">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC27">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE27">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK27">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,31 +4876,31 @@
         <v>1.73</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q28">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R28">
         <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
         <v>2.74</v>
       </c>
       <c r="U28">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.05</v>
@@ -4909,28 +4909,28 @@
         <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC28">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="O29">
-        <v>6.6</v>
+        <v>6.35</v>
       </c>
       <c r="P29">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>1.5</v>
       </c>
       <c r="R29">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U29">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="V29">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>5.9</v>
+        <v>5.45</v>
       </c>
       <c r="AA29">
         <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC29">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD29">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE29">
         <v>1.28</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG29">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AK29">
-        <v>4.25</v>
+        <v>3.98</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P30">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,52 +5362,52 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>3.6</v>
+        <v>3.89</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
         <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC31">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
         <v>1.48</v>
@@ -5419,7 +5419,7 @@
         <v>1.52</v>
       </c>
       <c r="AG31">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AK31">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,52 +5525,52 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O32">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="Q32">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T32">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U32">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA32">
         <v>2.13</v>
       </c>
       <c r="AB32">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD32">
         <v>1.22</v>
@@ -5579,7 +5579,7 @@
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
         <v>1.8</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O33">
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q33">
         <v>3.11</v>
       </c>
       <c r="R33">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5709,43 +5709,43 @@
         <v>3.38</v>
       </c>
       <c r="U33">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA33">
         <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AC33">
         <v>2.56</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE33">
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O34">
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
         <v>3.84</v>
@@ -5869,7 +5869,7 @@
         <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="U34">
         <v>3</v>
@@ -5884,13 +5884,13 @@
         <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
         <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB34">
         <v>1.7</v>
@@ -5902,13 +5902,13 @@
         <v>1.21</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="O35">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V35">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W35">
         <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
         <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,10 +6180,10 @@
         <v>3.25</v>
       </c>
       <c r="O36">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6512,71 +6512,71 @@
         <v>1.28</v>
       </c>
       <c r="Q38">
-        <v>8.25</v>
+        <v>8.4</v>
       </c>
       <c r="R38">
         <v>2.58</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
         <v>3.15</v>
       </c>
       <c r="U38">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
+        <v>1.16</v>
+      </c>
+      <c r="Z38">
+        <v>5.02</v>
+      </c>
+      <c r="AA38">
+        <v>1.54</v>
+      </c>
+      <c r="AB38">
+        <v>2.26</v>
+      </c>
+      <c r="AC38">
+        <v>2.35</v>
+      </c>
+      <c r="AD38">
+        <v>1.57</v>
+      </c>
+      <c r="AE38">
+        <v>1.22</v>
+      </c>
+      <c r="AF38">
+        <v>1.85</v>
+      </c>
+      <c r="AG38">
+        <v>1.81</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.12</v>
       </c>
-      <c r="Z38">
-        <v>4.7</v>
-      </c>
-      <c r="AA38">
-        <v>1.53</v>
-      </c>
-      <c r="AB38">
-        <v>2.28</v>
-      </c>
-      <c r="AC38">
-        <v>2.29</v>
-      </c>
-      <c r="AD38">
-        <v>1.43</v>
-      </c>
-      <c r="AE38">
-        <v>1.18</v>
-      </c>
-      <c r="AF38">
-        <v>1.75</v>
-      </c>
-      <c r="AG38">
-        <v>1.82</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>3.3</v>
-      </c>
       <c r="AK38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q39">
-        <v>3.05</v>
+        <v>2.07</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
+        <v>1.32</v>
+      </c>
+      <c r="T39">
+        <v>3.27</v>
+      </c>
+      <c r="U39">
+        <v>2.5</v>
+      </c>
+      <c r="V39">
+        <v>1.49</v>
+      </c>
+      <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4</v>
+      </c>
+      <c r="AA39">
+        <v>1.77</v>
+      </c>
+      <c r="AB39">
+        <v>2</v>
+      </c>
+      <c r="AC39">
+        <v>3.1</v>
+      </c>
+      <c r="AD39">
         <v>1.38</v>
       </c>
-      <c r="T39">
-        <v>2.7</v>
-      </c>
-      <c r="U39">
-        <v>2.75</v>
-      </c>
-      <c r="V39">
-        <v>1.39</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.05</v>
-      </c>
-      <c r="Y39">
-        <v>1.26</v>
-      </c>
-      <c r="Z39">
-        <v>3.2</v>
-      </c>
-      <c r="AA39">
-        <v>1.95</v>
-      </c>
-      <c r="AB39">
-        <v>1.81</v>
-      </c>
-      <c r="AC39">
-        <v>3.14</v>
-      </c>
-      <c r="AD39">
-        <v>1.27</v>
-      </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P40">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U40">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AC40">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>2.7</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -7007,19 +7007,19 @@
         <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
         <v>2.91</v>
       </c>
       <c r="U41">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V41">
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1</v>
@@ -7031,10 +7031,10 @@
         <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
         <v>2.74</v>
@@ -7043,13 +7043,13 @@
         <v>1.35</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK41">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T42">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="U42">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>4.46</v>
+        <v>3.3</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AC42">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="AD42">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,31 +7318,31 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="O43">
         <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2.55</v>
+        <v>3.73</v>
       </c>
       <c r="Q43">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="R43">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T43">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V43">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
         <v>1.17</v>
@@ -7351,31 +7351,31 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA43">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AC43">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AD43">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q46">
         <v>4.9</v>
@@ -7822,49 +7822,49 @@
         <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="U46">
         <v>2.13</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W46">
         <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
         <v>2.5</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD46">
         <v>1.62</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK46">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O47">
-        <v>5.4</v>
+        <v>4.85</v>
       </c>
       <c r="P47">
-        <v>7.6</v>
+        <v>7.25</v>
       </c>
       <c r="Q47">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="R47">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="S47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T47">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U47">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,28 +8006,28 @@
         <v>1.05</v>
       </c>
       <c r="Z47">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="AA47">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AB47">
-        <v>3.08</v>
+        <v>2.65</v>
       </c>
       <c r="AC47">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD47">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AE47">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF47">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK47">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB48">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8296,58 +8296,58 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O49">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q49">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U49">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V49">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W49">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA49">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AB49">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC49">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AD49">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE49">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF49">
         <v>1.41</v>
@@ -8369,7 +8369,7 @@
         <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>7.53</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
         <v>3.1</v>
       </c>
       <c r="P53">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
-        <v>3.39</v>
+        <v>3.06</v>
       </c>
       <c r="R53">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="S53">
         <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U53">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V53">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z53">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="AA53">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB53">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC53">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG53">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,13 +9114,13 @@
         <v>2.33</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R54">
         <v>2</v>
@@ -9132,7 +9132,7 @@
         <v>3.1</v>
       </c>
       <c r="U54">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V54">
         <v>1.48</v>
@@ -9144,31 +9144,31 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z54">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB54">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC54">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD54">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE54">
         <v>1.05</v>
       </c>
       <c r="AF54">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>1.88</v>
+      </c>
+      <c r="O55">
+        <v>3.25</v>
+      </c>
+      <c r="P55">
+        <v>3.5</v>
+      </c>
+      <c r="Q55">
+        <v>2.5</v>
+      </c>
+      <c r="R55">
+        <v>2.15</v>
+      </c>
+      <c r="S55">
+        <v>1.39</v>
+      </c>
+      <c r="T55">
+        <v>2.66</v>
+      </c>
+      <c r="U55">
+        <v>2.81</v>
+      </c>
+      <c r="V55">
+        <v>1.38</v>
+      </c>
+      <c r="W55">
+        <v>1.07</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
+        <v>3.5</v>
+      </c>
+      <c r="AA55">
+        <v>1.97</v>
+      </c>
+      <c r="AB55">
+        <v>1.82</v>
+      </c>
+      <c r="AC55">
+        <v>3.35</v>
+      </c>
+      <c r="AD55">
+        <v>1.24</v>
+      </c>
+      <c r="AE55">
+        <v>1.06</v>
+      </c>
+      <c r="AF55">
         <v>1.75</v>
       </c>
-      <c r="O55">
-        <v>3.4</v>
-      </c>
-      <c r="P55">
-        <v>4.11</v>
-      </c>
-      <c r="Q55">
-        <v>2.32</v>
-      </c>
-      <c r="R55">
-        <v>2.2</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
-      </c>
-      <c r="Y55">
-        <v>0</v>
-      </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-      <c r="AA55">
-        <v>2</v>
-      </c>
-      <c r="AB55">
-        <v>1.8</v>
-      </c>
-      <c r="AC55">
-        <v>0</v>
-      </c>
-      <c r="AD55">
-        <v>0</v>
-      </c>
-      <c r="AE55">
-        <v>0</v>
-      </c>
-      <c r="AF55">
-        <v>1.94</v>
-      </c>
       <c r="AG55">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9603,40 +9603,40 @@
         <v>2.7</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
         <v>1.53</v>
@@ -9645,19 +9645,19 @@
         <v>2.37</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -964,10 +964,10 @@
         <v>1.66</v>
       </c>
       <c r="O4">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>4.82</v>
+        <v>4.35</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -976,13 +976,13 @@
         <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="U4">
-        <v>2.96</v>
+        <v>3.16</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -991,22 +991,22 @@
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
         <v>1.41</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA4">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB4">
         <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="AD4">
         <v>1.18</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
         <v>2.03</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="Q6">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1305,43 +1305,43 @@
         <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U6">
         <v>3.1</v>
       </c>
       <c r="V6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y6">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AA6">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC6">
         <v>4.33</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG6">
         <v>1.75</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="O7">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="P7">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q7">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R7">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U7">
         <v>2.25</v>
@@ -1477,7 +1477,7 @@
         <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.03</v>
@@ -1486,25 +1486,25 @@
         <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC7">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD7">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
         <v>1.8</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AK7">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>2.37</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V10">
+        <v>1.41</v>
+      </c>
+      <c r="W10">
+        <v>1.07</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.25</v>
+      </c>
+      <c r="Z10">
+        <v>3.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.78</v>
+      </c>
+      <c r="AB10">
+        <v>1.91</v>
+      </c>
+      <c r="AC10">
+        <v>3.1</v>
+      </c>
+      <c r="AD10">
         <v>1.33</v>
       </c>
-      <c r="W10">
-        <v>1.08</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.3</v>
-      </c>
-      <c r="Z10">
-        <v>3.22</v>
-      </c>
-      <c r="AA10">
-        <v>1.93</v>
-      </c>
-      <c r="AB10">
-        <v>1.74</v>
-      </c>
-      <c r="AC10">
-        <v>3.6</v>
-      </c>
-      <c r="AD10">
-        <v>1.23</v>
-      </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
+        <v>1.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.25</v>
+      </c>
+      <c r="AK10">
         <v>2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.47</v>
-      </c>
-      <c r="AK10">
-        <v>1.35</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="R11">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="S11">
+        <v>1.36</v>
+      </c>
+      <c r="T11">
+        <v>2.88</v>
+      </c>
+      <c r="U11">
+        <v>2.88</v>
+      </c>
+      <c r="V11">
         <v>1.33</v>
       </c>
-      <c r="T11">
-        <v>3</v>
-      </c>
-      <c r="U11">
-        <v>2.56</v>
-      </c>
-      <c r="V11">
-        <v>1.41</v>
-      </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AA11">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AB11">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AK11">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
+        <v>3.89</v>
+      </c>
+      <c r="O15">
+        <v>3.6</v>
+      </c>
+      <c r="P15">
+        <v>1.78</v>
+      </c>
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="R15">
+        <v>2.5</v>
+      </c>
+      <c r="S15">
+        <v>1.25</v>
+      </c>
+      <c r="T15">
+        <v>3.6</v>
+      </c>
+      <c r="U15">
+        <v>2.25</v>
+      </c>
+      <c r="V15">
+        <v>1.6</v>
+      </c>
+      <c r="W15">
+        <v>1.12</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.13</v>
+      </c>
+      <c r="Z15">
+        <v>5.5</v>
+      </c>
+      <c r="AA15">
+        <v>1.5</v>
+      </c>
+      <c r="AB15">
         <v>2.4</v>
       </c>
-      <c r="O15">
-        <v>3.4</v>
-      </c>
-      <c r="P15">
-        <v>2.64</v>
-      </c>
-      <c r="Q15">
-        <v>2.75</v>
-      </c>
-      <c r="R15">
-        <v>2.26</v>
-      </c>
-      <c r="S15">
-        <v>1.28</v>
-      </c>
-      <c r="T15">
-        <v>3.25</v>
-      </c>
-      <c r="U15">
-        <v>2.45</v>
-      </c>
-      <c r="V15">
-        <v>1.47</v>
-      </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.22</v>
-      </c>
-      <c r="Z15">
-        <v>4</v>
-      </c>
-      <c r="AA15">
-        <v>1.7</v>
-      </c>
-      <c r="AB15">
-        <v>2.15</v>
-      </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG15">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
+        <v>1.2</v>
+      </c>
+      <c r="AK15">
         <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O16">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
         <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.89</v>
+        <v>2.12</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P17">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
+        <v>1.16</v>
+      </c>
+      <c r="Z17">
+        <v>4.05</v>
+      </c>
+      <c r="AA17">
+        <v>1.66</v>
+      </c>
+      <c r="AB17">
+        <v>2.15</v>
+      </c>
+      <c r="AC17">
+        <v>2.52</v>
+      </c>
+      <c r="AD17">
+        <v>1.41</v>
+      </c>
+      <c r="AE17">
         <v>1.13</v>
       </c>
-      <c r="Z17">
-        <v>5.5</v>
-      </c>
-      <c r="AA17">
-        <v>1.5</v>
-      </c>
-      <c r="AB17">
-        <v>2.4</v>
-      </c>
-      <c r="AC17">
-        <v>2.35</v>
-      </c>
-      <c r="AD17">
-        <v>1.57</v>
-      </c>
-      <c r="AE17">
-        <v>1.19</v>
-      </c>
       <c r="AF17">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
         <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="S19">
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,13 +3439,13 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="AA19">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB19">
         <v>2.2</v>
@@ -3454,16 +3454,16 @@
         <v>2.62</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,16 +3572,16 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
         <v>4.4</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3599,31 +3599,31 @@
         <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA20">
         <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC20">
         <v>2.14</v>
       </c>
       <c r="AD20">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AE20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG20">
         <v>2.45</v>
@@ -3738,13 +3738,13 @@
         <v>6.5</v>
       </c>
       <c r="P21">
-        <v>13</v>
+        <v>8.56</v>
       </c>
       <c r="Q21">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R21">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="S21">
         <v>1.14</v>
@@ -3753,13 +3753,13 @@
         <v>4.8</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V21">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,25 +3771,25 @@
         <v>6.5</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB21">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AC21">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AD21">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE21">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK21">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
-        <v>4.9</v>
+        <v>5.64</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC26">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD26">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE26">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG26">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5.64</v>
+        <v>4.9</v>
       </c>
       <c r="AA27">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD27">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE27">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q35">
         <v>3.13</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="S35">
         <v>1.29</v>
@@ -6035,10 +6035,10 @@
         <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
         <v>1.08</v>
@@ -6062,16 +6062,16 @@
         <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE35">
         <v>1.12</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,43 +6177,43 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P36">
         <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA36">
         <v>2.2</v>
@@ -6222,19 +6222,19 @@
         <v>1.65</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O37">
         <v>4.4</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q37">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R37">
         <v>2.55</v>
@@ -6358,16 +6358,16 @@
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6379,25 +6379,25 @@
         <v>4.65</v>
       </c>
       <c r="AA37">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AC37">
         <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE37">
         <v>1.23</v>
       </c>
       <c r="AF37">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>5.02</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AB38">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="AD38">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AK38">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q39">
-        <v>2.07</v>
+        <v>3.08</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD39">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.31</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>1.28</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>8.4</v>
       </c>
       <c r="R40">
+        <v>2.58</v>
+      </c>
+      <c r="S40">
+        <v>1.28</v>
+      </c>
+      <c r="T40">
+        <v>3.15</v>
+      </c>
+      <c r="U40">
         <v>2.25</v>
       </c>
-      <c r="S40">
-        <v>1.33</v>
-      </c>
-      <c r="T40">
-        <v>3.08</v>
-      </c>
-      <c r="U40">
-        <v>2.4</v>
-      </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>5.02</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AB40">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AC40">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
+        <v>1.22</v>
+      </c>
+      <c r="AF40">
+        <v>1.85</v>
+      </c>
+      <c r="AG40">
+        <v>1.81</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.12</v>
       </c>
-      <c r="AF40">
-        <v>1.5</v>
-      </c>
-      <c r="AG40">
-        <v>2.35</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.3</v>
-      </c>
       <c r="AK40">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
         <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
         <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA41">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AD41">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="O42">
+        <v>3.75</v>
+      </c>
+      <c r="P42">
+        <v>4.4</v>
+      </c>
+      <c r="Q42">
+        <v>2.07</v>
+      </c>
+      <c r="R42">
+        <v>2.3</v>
+      </c>
+      <c r="S42">
+        <v>1.32</v>
+      </c>
+      <c r="T42">
+        <v>3.27</v>
+      </c>
+      <c r="U42">
+        <v>2.5</v>
+      </c>
+      <c r="V42">
+        <v>1.49</v>
+      </c>
+      <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.18</v>
+      </c>
+      <c r="Z42">
+        <v>4</v>
+      </c>
+      <c r="AA42">
+        <v>1.77</v>
+      </c>
+      <c r="AB42">
+        <v>2</v>
+      </c>
+      <c r="AC42">
         <v>3.1</v>
       </c>
-      <c r="P42">
-        <v>2.85</v>
-      </c>
-      <c r="Q42">
-        <v>3.08</v>
-      </c>
-      <c r="R42">
+      <c r="AD42">
+        <v>1.38</v>
+      </c>
+      <c r="AE42">
+        <v>1.14</v>
+      </c>
+      <c r="AF42">
+        <v>1.63</v>
+      </c>
+      <c r="AG42">
         <v>2.06</v>
       </c>
-      <c r="S42">
-        <v>1.38</v>
-      </c>
-      <c r="T42">
-        <v>2.7</v>
-      </c>
-      <c r="U42">
-        <v>2.75</v>
-      </c>
-      <c r="V42">
-        <v>1.36</v>
-      </c>
-      <c r="W42">
-        <v>1.08</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.29</v>
-      </c>
-      <c r="Z42">
-        <v>3.3</v>
-      </c>
-      <c r="AA42">
-        <v>1.97</v>
-      </c>
-      <c r="AB42">
-        <v>1.81</v>
-      </c>
-      <c r="AC42">
-        <v>3.14</v>
-      </c>
-      <c r="AD42">
-        <v>1.27</v>
-      </c>
-      <c r="AE42">
-        <v>1.06</v>
-      </c>
-      <c r="AF42">
-        <v>1.7</v>
-      </c>
-      <c r="AG42">
-        <v>2.05</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="O44">
         <v>3.5</v>
       </c>
       <c r="P44">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q44">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R44">
         <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W44">
         <v>1.05</v>
@@ -7517,41 +7517,41 @@
         <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC44">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="AD44">
+        <v>1.24</v>
+      </c>
+      <c r="AE44">
+        <v>1.06</v>
+      </c>
+      <c r="AF44">
+        <v>1.83</v>
+      </c>
+      <c r="AG44">
+        <v>1.85</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.1</v>
-      </c>
-      <c r="AF44">
-        <v>1.84</v>
-      </c>
-      <c r="AG44">
-        <v>1.86</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.29</v>
       </c>
       <c r="AK44">
         <v>1.2</v>
@@ -7647,31 +7647,31 @@
         <v>1.25</v>
       </c>
       <c r="O45">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="P45">
-        <v>10.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q45">
         <v>1.57</v>
       </c>
       <c r="R45">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="S45">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T45">
         <v>4.75</v>
       </c>
       <c r="U45">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V45">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7689,19 +7689,19 @@
         <v>3.2</v>
       </c>
       <c r="AC45">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AD45">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AE45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF45">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG45">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK45">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q50">
         <v>2.06</v>
       </c>
       <c r="R50">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA50">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF50">
         <v>1.68</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O51">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="Q51">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R51">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="U51">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
         <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC51">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8954,10 +8954,10 @@
         <v>3.1</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="R53">
         <v>1.93</v>
@@ -8993,13 +8993,13 @@
         <v>1.79</v>
       </c>
       <c r="AC53">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD53">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
         <v>1.57</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O56">
         <v>3.28</v>
       </c>
       <c r="P56">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S56">
         <v>1.33</v>
@@ -9458,7 +9458,7 @@
         <v>3</v>
       </c>
       <c r="U56">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V56">
         <v>1.4</v>
@@ -9476,10 +9476,10 @@
         <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB56">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC56">
         <v>3.15</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.89</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>1.78</v>
+        <v>2.64</v>
       </c>
       <c r="Q15">
+        <v>2.75</v>
+      </c>
+      <c r="R15">
+        <v>2.26</v>
+      </c>
+      <c r="S15">
+        <v>1.28</v>
+      </c>
+      <c r="T15">
+        <v>3.25</v>
+      </c>
+      <c r="U15">
+        <v>2.45</v>
+      </c>
+      <c r="V15">
+        <v>1.47</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.04</v>
+      </c>
+      <c r="Y15">
+        <v>1.22</v>
+      </c>
+      <c r="Z15">
         <v>4</v>
       </c>
-      <c r="R15">
-        <v>2.5</v>
-      </c>
-      <c r="S15">
+      <c r="AA15">
+        <v>1.7</v>
+      </c>
+      <c r="AB15">
+        <v>2.15</v>
+      </c>
+      <c r="AC15">
+        <v>2.62</v>
+      </c>
+      <c r="AD15">
+        <v>1.38</v>
+      </c>
+      <c r="AE15">
+        <v>1.11</v>
+      </c>
+      <c r="AF15">
+        <v>1.55</v>
+      </c>
+      <c r="AG15">
+        <v>2.28</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.25</v>
       </c>
-      <c r="T15">
-        <v>3.6</v>
-      </c>
-      <c r="U15">
-        <v>2.25</v>
-      </c>
-      <c r="V15">
+      <c r="AK15">
         <v>1.6</v>
-      </c>
-      <c r="W15">
-        <v>1.12</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.13</v>
-      </c>
-      <c r="Z15">
-        <v>5.5</v>
-      </c>
-      <c r="AA15">
-        <v>1.5</v>
-      </c>
-      <c r="AB15">
-        <v>2.4</v>
-      </c>
-      <c r="AC15">
-        <v>2.35</v>
-      </c>
-      <c r="AD15">
-        <v>1.57</v>
-      </c>
-      <c r="AE15">
-        <v>1.19</v>
-      </c>
-      <c r="AF15">
-        <v>1.51</v>
-      </c>
-      <c r="AG15">
-        <v>2.39</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.2</v>
-      </c>
-      <c r="AK15">
-        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>3.89</v>
+      </c>
+      <c r="O16">
+        <v>3.6</v>
+      </c>
+      <c r="P16">
+        <v>1.78</v>
+      </c>
+      <c r="Q16">
+        <v>4</v>
+      </c>
+      <c r="R16">
+        <v>2.5</v>
+      </c>
+      <c r="S16">
+        <v>1.25</v>
+      </c>
+      <c r="T16">
+        <v>3.6</v>
+      </c>
+      <c r="U16">
+        <v>2.25</v>
+      </c>
+      <c r="V16">
+        <v>1.6</v>
+      </c>
+      <c r="W16">
+        <v>1.12</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.13</v>
+      </c>
+      <c r="Z16">
+        <v>5.5</v>
+      </c>
+      <c r="AA16">
+        <v>1.5</v>
+      </c>
+      <c r="AB16">
         <v>2.4</v>
       </c>
-      <c r="O16">
-        <v>3.4</v>
-      </c>
-      <c r="P16">
-        <v>2.64</v>
-      </c>
-      <c r="Q16">
-        <v>2.75</v>
-      </c>
-      <c r="R16">
-        <v>2.26</v>
-      </c>
-      <c r="S16">
-        <v>1.28</v>
-      </c>
-      <c r="T16">
-        <v>3.25</v>
-      </c>
-      <c r="U16">
-        <v>2.45</v>
-      </c>
-      <c r="V16">
-        <v>1.47</v>
-      </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.22</v>
-      </c>
-      <c r="Z16">
-        <v>4</v>
-      </c>
-      <c r="AA16">
-        <v>1.7</v>
-      </c>
-      <c r="AB16">
-        <v>2.15</v>
-      </c>
       <c r="AC16">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG16">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
+        <v>1.2</v>
+      </c>
+      <c r="AK16">
         <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.6</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.77</v>
+        <v>2.23</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="R25">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U25">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA25">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC25">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AD25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF25">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AG25">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
         <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
         <v>1.14</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>5.64</v>
+        <v>4.95</v>
       </c>
       <c r="AA26">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB26">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AC26">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD26">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE26">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG26">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q27">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z27">
-        <v>4.9</v>
+        <v>5.64</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC27">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AD27">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE27">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
+        <v>2.4</v>
+      </c>
+      <c r="O38">
+        <v>3.1</v>
+      </c>
+      <c r="P38">
+        <v>2.85</v>
+      </c>
+      <c r="Q38">
+        <v>3.08</v>
+      </c>
+      <c r="R38">
+        <v>2.06</v>
+      </c>
+      <c r="S38">
+        <v>1.38</v>
+      </c>
+      <c r="T38">
         <v>2.7</v>
       </c>
-      <c r="O38">
+      <c r="U38">
+        <v>2.75</v>
+      </c>
+      <c r="V38">
+        <v>1.36</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.29</v>
+      </c>
+      <c r="Z38">
         <v>3.3</v>
       </c>
-      <c r="P38">
-        <v>2.2</v>
-      </c>
-      <c r="Q38">
-        <v>3.25</v>
-      </c>
-      <c r="R38">
-        <v>2.25</v>
-      </c>
-      <c r="S38">
-        <v>1.3</v>
-      </c>
-      <c r="T38">
-        <v>2.91</v>
-      </c>
-      <c r="U38">
-        <v>2.48</v>
-      </c>
-      <c r="V38">
-        <v>1.44</v>
-      </c>
-      <c r="W38">
-        <v>1.11</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1.19</v>
-      </c>
-      <c r="Z38">
-        <v>3.8</v>
-      </c>
       <c r="AA38">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AB38">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AC38">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
+        <v>1.24</v>
+      </c>
+      <c r="AK38">
         <v>1.53</v>
-      </c>
-      <c r="AK38">
-        <v>1.26</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>2.31</v>
+      </c>
+      <c r="O39">
+        <v>3.45</v>
+      </c>
+      <c r="P39">
+        <v>2.75</v>
+      </c>
+      <c r="Q39">
+        <v>2.88</v>
+      </c>
+      <c r="R39">
+        <v>2.25</v>
+      </c>
+      <c r="S39">
+        <v>1.33</v>
+      </c>
+      <c r="T39">
+        <v>3.08</v>
+      </c>
+      <c r="U39">
         <v>2.4</v>
       </c>
-      <c r="O39">
-        <v>3.1</v>
-      </c>
-      <c r="P39">
-        <v>2.85</v>
-      </c>
-      <c r="Q39">
-        <v>3.08</v>
-      </c>
-      <c r="R39">
-        <v>2.06</v>
-      </c>
-      <c r="S39">
-        <v>1.38</v>
-      </c>
-      <c r="T39">
-        <v>2.7</v>
-      </c>
-      <c r="U39">
-        <v>2.75</v>
-      </c>
       <c r="V39">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA39">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="AC39">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="AD39">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q40">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z40">
-        <v>5.02</v>
+        <v>3.8</v>
       </c>
       <c r="AA40">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AB40">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AC40">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="AD40">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AK40">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.31</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>1.28</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>8.4</v>
       </c>
       <c r="R41">
+        <v>2.58</v>
+      </c>
+      <c r="S41">
+        <v>1.28</v>
+      </c>
+      <c r="T41">
+        <v>3.15</v>
+      </c>
+      <c r="U41">
         <v>2.25</v>
       </c>
-      <c r="S41">
-        <v>1.33</v>
-      </c>
-      <c r="T41">
-        <v>3.08</v>
-      </c>
-      <c r="U41">
-        <v>2.4</v>
-      </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
         <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>4.2</v>
+        <v>5.02</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AC41">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE41">
+        <v>1.22</v>
+      </c>
+      <c r="AF41">
+        <v>1.85</v>
+      </c>
+      <c r="AG41">
+        <v>1.81</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.12</v>
       </c>
-      <c r="AF41">
-        <v>1.5</v>
-      </c>
-      <c r="AG41">
-        <v>2.35</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.3</v>
-      </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -627,24 +627,24 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
         <v>1.83</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q2">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
         <v>2.38</v>
@@ -656,52 +656,52 @@
         <v>3.55</v>
       </c>
       <c r="U2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.57</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="AA2">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AB2">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC2">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AD2">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF2">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG2">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P15">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="Q15">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
         <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
         <v>2.15</v>
       </c>
       <c r="AC17">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD17">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
         <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S26">
         <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="U26">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
         <v>1.14</v>
@@ -4580,31 +4580,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
-        <v>4.95</v>
+        <v>5.64</v>
       </c>
       <c r="AA26">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AC26">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AD26">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE26">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF26">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P27">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="Q27">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S27">
         <v>1.2</v>
       </c>
       <c r="T27">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>5.64</v>
+        <v>4.95</v>
       </c>
       <c r="AA27">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB27">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="AC27">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD27">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB38">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="AD38">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="O39">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
+        <v>2.85</v>
+      </c>
+      <c r="Q39">
+        <v>3.08</v>
+      </c>
+      <c r="R39">
+        <v>2.06</v>
+      </c>
+      <c r="S39">
+        <v>1.38</v>
+      </c>
+      <c r="T39">
+        <v>2.7</v>
+      </c>
+      <c r="U39">
         <v>2.75</v>
       </c>
-      <c r="Q39">
-        <v>2.88</v>
-      </c>
-      <c r="R39">
-        <v>2.25</v>
-      </c>
-      <c r="S39">
-        <v>1.33</v>
-      </c>
-      <c r="T39">
-        <v>3.08</v>
-      </c>
-      <c r="U39">
-        <v>2.4</v>
-      </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="AB39">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P40">
-        <v>2.2</v>
+        <v>1.28</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="R40">
+        <v>2.58</v>
+      </c>
+      <c r="S40">
+        <v>1.28</v>
+      </c>
+      <c r="T40">
+        <v>3.15</v>
+      </c>
+      <c r="U40">
         <v>2.25</v>
       </c>
-      <c r="S40">
-        <v>1.3</v>
-      </c>
-      <c r="T40">
-        <v>2.91</v>
-      </c>
-      <c r="U40">
-        <v>2.48</v>
-      </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>3.8</v>
+        <v>5.02</v>
       </c>
       <c r="AA40">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AB40">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AC40">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>2.21</v>
+        <v>1.81</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>10</v>
+        <v>2.31</v>
       </c>
       <c r="O41">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>1.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>8.4</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U41">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
         <v>1.16</v>
       </c>
       <c r="Z41">
-        <v>5.02</v>
+        <v>4.2</v>
       </c>
       <c r="AA41">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AC41">
+        <v>2.65</v>
+      </c>
+      <c r="AD41">
+        <v>1.4</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
+        <v>1.5</v>
+      </c>
+      <c r="AG41">
         <v>2.35</v>
       </c>
-      <c r="AD41">
-        <v>1.57</v>
-      </c>
-      <c r="AE41">
-        <v>1.22</v>
-      </c>
-      <c r="AF41">
-        <v>1.85</v>
-      </c>
-      <c r="AG41">
-        <v>1.81</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,45 +787,45 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
         <v>2.6</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
         <v>2.63</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -837,7 +837,7 @@
         <v>3.9</v>
       </c>
       <c r="AA3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB3">
         <v>2</v>
@@ -852,14 +852,14 @@
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
         <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -868,37 +868,37 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P4">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
         <v>2.1</v>
@@ -982,37 +982,37 @@
         <v>2.62</v>
       </c>
       <c r="U4">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AA4">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.21</v>
+        <v>3.7</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
         <v>2.05</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK4">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.78</v>
       </c>
       <c r="V5">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA5">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="AC5">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="AD5">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AG5">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1305,40 +1305,40 @@
         <v>1.42</v>
       </c>
       <c r="T6">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X6">
         <v>1.09</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA6">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB6">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC6">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
         <v>1.98</v>
@@ -1360,7 +1360,7 @@
         <v>1.53</v>
       </c>
       <c r="AK6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
         <v>3.7</v>
       </c>
       <c r="P8">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>2.34</v>
@@ -1631,7 +1631,7 @@
         <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="U8">
         <v>2.1</v>
@@ -1643,13 +1643,13 @@
         <v>1.17</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.08</v>
       </c>
       <c r="Z8">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="AA8">
         <v>1.39</v>
@@ -1658,19 +1658,19 @@
         <v>2.5</v>
       </c>
       <c r="AC8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG8">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="P9">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="Q9">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S9">
         <v>1.36</v>
@@ -1797,47 +1797,47 @@
         <v>2.8</v>
       </c>
       <c r="U9">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="V9">
+        <v>1.33</v>
+      </c>
+      <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
         <v>1.3</v>
       </c>
-      <c r="W9">
-        <v>1.02</v>
-      </c>
-      <c r="X9">
-        <v>1.02</v>
-      </c>
-      <c r="Y9">
-        <v>1.33</v>
-      </c>
       <c r="Z9">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
         <v>1.73</v>
       </c>
       <c r="AG9">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1846,37 +1846,37 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,79 +1928,79 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
         <v>4</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="R10">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA10">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AB10">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG10">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2009,37 +2009,37 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
+        <v>2.2</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>1</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>14</v>
+      </c>
+      <c r="AP10">
         <v>2</v>
       </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>-1</v>
-      </c>
-      <c r="AN10">
-        <v>-1</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>-1</v>
-      </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2091,118 +2091,118 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
         <v>2.62</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q11">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R11">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
+        <v>3.08</v>
+      </c>
+      <c r="U11">
+        <v>2.4</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.2</v>
+      </c>
+      <c r="Z11">
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <v>1.7</v>
+      </c>
+      <c r="AB11">
+        <v>2.01</v>
+      </c>
+      <c r="AC11">
+        <v>2.74</v>
+      </c>
+      <c r="AD11">
+        <v>1.35</v>
+      </c>
+      <c r="AE11">
+        <v>1.1</v>
+      </c>
+      <c r="AF11">
+        <v>1.57</v>
+      </c>
+      <c r="AG11">
+        <v>2.2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>["81"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.53</v>
+      </c>
+      <c r="AK11">
         <v>1.36</v>
       </c>
-      <c r="T11">
-        <v>2.88</v>
-      </c>
-      <c r="U11">
-        <v>2.88</v>
-      </c>
-      <c r="V11">
-        <v>1.33</v>
-      </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <v>6</v>
+      </c>
+      <c r="AO11">
+        <v>7</v>
+      </c>
+      <c r="AP11">
+        <v>13</v>
+      </c>
+      <c r="AQ11">
         <v>1.01</v>
       </c>
-      <c r="Y11">
-        <v>1.3</v>
-      </c>
-      <c r="Z11">
-        <v>3.22</v>
-      </c>
-      <c r="AA11">
-        <v>1.93</v>
-      </c>
-      <c r="AB11">
-        <v>1.74</v>
-      </c>
-      <c r="AC11">
-        <v>3.6</v>
-      </c>
-      <c r="AD11">
-        <v>1.23</v>
-      </c>
-      <c r="AE11">
-        <v>1.06</v>
-      </c>
-      <c r="AF11">
-        <v>1.74</v>
-      </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.47</v>
-      </c>
-      <c r="AK11">
-        <v>1.35</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-1</v>
-      </c>
-      <c r="AN11">
-        <v>-1</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>-1</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,111 +2261,111 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>3.11</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
         <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AA12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC12">
         <v>3.4</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
         <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AJ12">
         <v>1.5</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.45</v>
+        <v>1.96</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P14">
-        <v>2.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>3.95</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S14">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U14">
+        <v>2.25</v>
+      </c>
+      <c r="V14">
+        <v>1.59</v>
+      </c>
+      <c r="W14">
+        <v>1.12</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
+        <v>1.13</v>
+      </c>
+      <c r="Z14">
+        <v>4.75</v>
+      </c>
+      <c r="AA14">
+        <v>1.57</v>
+      </c>
+      <c r="AB14">
         <v>2.35</v>
       </c>
-      <c r="V14">
-        <v>1.54</v>
-      </c>
-      <c r="W14">
-        <v>1.08</v>
-      </c>
-      <c r="X14">
-        <v>1.02</v>
-      </c>
-      <c r="Y14">
+      <c r="AC14">
+        <v>2.35</v>
+      </c>
+      <c r="AD14">
+        <v>1.61</v>
+      </c>
+      <c r="AE14">
         <v>1.2</v>
       </c>
-      <c r="Z14">
-        <v>4.5</v>
-      </c>
-      <c r="AA14">
-        <v>1.64</v>
-      </c>
-      <c r="AB14">
-        <v>2.19</v>
-      </c>
-      <c r="AC14">
-        <v>2.49</v>
-      </c>
-      <c r="AD14">
-        <v>1.42</v>
-      </c>
-      <c r="AE14">
-        <v>1.14</v>
-      </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA15">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AC15">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.89</v>
+        <v>3.55</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P16">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Q16">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R16">
+        <v>2.3</v>
+      </c>
+      <c r="S16">
+        <v>1.29</v>
+      </c>
+      <c r="T16">
+        <v>3.4</v>
+      </c>
+      <c r="U16">
         <v>2.5</v>
       </c>
-      <c r="S16">
-        <v>1.25</v>
-      </c>
-      <c r="T16">
-        <v>3.6</v>
-      </c>
-      <c r="U16">
-        <v>2.25</v>
-      </c>
       <c r="V16">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="W16">
         <v>1.12</v>
@@ -2950,31 +2950,31 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA16">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
         <v>1.19</v>
       </c>
       <c r="AF16">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AG16">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,55 +3080,55 @@
         </is>
       </c>
       <c r="N17">
+        <v>1.85</v>
+      </c>
+      <c r="O17">
+        <v>3.5</v>
+      </c>
+      <c r="P17">
+        <v>3.4</v>
+      </c>
+      <c r="Q17">
         <v>2.4</v>
       </c>
-      <c r="O17">
-        <v>3.4</v>
-      </c>
-      <c r="P17">
-        <v>2.64</v>
-      </c>
-      <c r="Q17">
-        <v>2.75</v>
-      </c>
       <c r="R17">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
         <v>3.25</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
@@ -3137,7 +3137,7 @@
         <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P18">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R18">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
         <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
         <v>2.25</v>
       </c>
       <c r="V18">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,28 +3279,28 @@
         <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>5.4</v>
+        <v>5.03</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AD18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="O22">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q22">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="R22">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S22">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="U22">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
+        <v>1.33</v>
+      </c>
+      <c r="W22">
+        <v>1.02</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
         <v>1.35</v>
       </c>
-      <c r="W22">
-        <v>1.03</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
-        <v>1.33</v>
-      </c>
       <c r="Z22">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="AA22">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AB22">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q23">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="R23">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S23">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.3</v>
+      </c>
+      <c r="Z23">
+        <v>2.97</v>
+      </c>
+      <c r="AA23">
+        <v>2.09</v>
+      </c>
+      <c r="AB23">
+        <v>1.69</v>
+      </c>
+      <c r="AC23">
+        <v>3.65</v>
+      </c>
+      <c r="AD23">
         <v>1.22</v>
       </c>
-      <c r="Z23">
-        <v>3.5</v>
-      </c>
-      <c r="AA23">
-        <v>1.82</v>
-      </c>
-      <c r="AB23">
-        <v>1.85</v>
-      </c>
-      <c r="AC23">
-        <v>2.95</v>
-      </c>
-      <c r="AD23">
-        <v>1.29</v>
-      </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK23">
         <v>1.33</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>4.95</v>
+        <v>5.44</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4245,7 +4245,7 @@
         <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
         <v>1.08</v>
@@ -4257,28 +4257,28 @@
         <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB24">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC24">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="AD24">
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="P25">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q25">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U25">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA25">
+        <v>1.54</v>
+      </c>
+      <c r="AB25">
+        <v>2.35</v>
+      </c>
+      <c r="AC25">
+        <v>2.27</v>
+      </c>
+      <c r="AD25">
+        <v>1.53</v>
+      </c>
+      <c r="AE25">
+        <v>1.24</v>
+      </c>
+      <c r="AF25">
         <v>1.5</v>
       </c>
-      <c r="AB25">
-        <v>2.43</v>
-      </c>
-      <c r="AC25">
-        <v>2.16</v>
-      </c>
-      <c r="AD25">
-        <v>1.6</v>
-      </c>
-      <c r="AE25">
-        <v>1.26</v>
-      </c>
-      <c r="AF25">
-        <v>1.41</v>
-      </c>
       <c r="AG25">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
         <v>2.88</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T26">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U26">
         <v>2.1</v>
@@ -4574,37 +4574,37 @@
         <v>1.65</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>5.64</v>
+        <v>5.53</v>
       </c>
       <c r="AA26">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB26">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="AC26">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD26">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE26">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
         <v>1.4</v>
       </c>
       <c r="AG26">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="Q27">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="R27">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U27">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA27">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AC27">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD27">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R28">
         <v>2.1</v>
@@ -4891,16 +4891,16 @@
         <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.05</v>
@@ -4918,19 +4918,19 @@
         <v>1.85</v>
       </c>
       <c r="AC28">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD28">
         <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
         <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.14</v>
       </c>
       <c r="AK28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O29">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Q29">
         <v>1.5</v>
@@ -5051,19 +5051,19 @@
         <v>2.88</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="V29">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5072,13 +5072,13 @@
         <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>5.45</v>
+        <v>6.05</v>
       </c>
       <c r="AA29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AC29">
         <v>2.05</v>
@@ -5087,13 +5087,13 @@
         <v>1.73</v>
       </c>
       <c r="AE29">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG29">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
         <v>3.98</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>5.09</v>
+        <v>4.8</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA30">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="O31">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q31">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="R31">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
         <v>1.11</v>
@@ -5395,31 +5395,31 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
         <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AB31">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE31">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="Q32">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="S32">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V32">
         <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z32">
         <v>2.9</v>
       </c>
       <c r="AA32">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AB32">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AC32">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD32">
         <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
         <v>3.11</v>
@@ -5709,37 +5709,37 @@
         <v>3.38</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
         <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC33">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD33">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
         <v>1.57</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="O34">
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="R34">
         <v>2</v>
       </c>
       <c r="S34">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T34">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="U34">
         <v>3</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5884,31 +5884,31 @@
         <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA34">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD34">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,58 +6020,58 @@
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q35">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="R35">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="V35">
+        <v>1.51</v>
+      </c>
+      <c r="W35">
+        <v>1.11</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.2</v>
+      </c>
+      <c r="Z35">
+        <v>4.4</v>
+      </c>
+      <c r="AA35">
+        <v>1.66</v>
+      </c>
+      <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.65</v>
+      </c>
+      <c r="AD35">
+        <v>1.43</v>
+      </c>
+      <c r="AE35">
+        <v>1.15</v>
+      </c>
+      <c r="AF35">
         <v>1.5</v>
       </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.22</v>
-      </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
-        <v>1.7</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
-      <c r="AC35">
-        <v>2.59</v>
-      </c>
-      <c r="AD35">
-        <v>1.48</v>
-      </c>
-      <c r="AE35">
-        <v>1.12</v>
-      </c>
-      <c r="AF35">
-        <v>1.55</v>
-      </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6180,61 +6180,61 @@
         <v>3.3</v>
       </c>
       <c r="O36">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
         <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="U36">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z36">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AB36">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC36">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="AD36">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG36">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P38">
         <v>2.2</v>
@@ -6518,49 +6518,49 @@
         <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="U38">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA38">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB38">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AC38">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
         <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AK38">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="Q39">
-        <v>3.08</v>
+        <v>2.78</v>
       </c>
       <c r="R39">
         <v>2.06</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
         <v>2.7</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
         <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
         <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AB39">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="AD39">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
         <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK39">
         <v>1.53</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>10</v>
+        <v>2.34</v>
       </c>
       <c r="O40">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>1.28</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>8.4</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>5.02</v>
+        <v>3.85</v>
       </c>
       <c r="AA40">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AB40">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
+        <v>1.36</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
         <v>1.57</v>
       </c>
-      <c r="AE40">
+      <c r="AG40">
+        <v>2.2</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.22</v>
       </c>
-      <c r="AF40">
-        <v>1.85</v>
-      </c>
-      <c r="AG40">
-        <v>1.81</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.12</v>
-      </c>
       <c r="AK40">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.31</v>
+        <v>9.5</v>
       </c>
       <c r="O41">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>7.74</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="S41">
         <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AG41">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,37 +7155,37 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>4.4</v>
+        <v>4.71</v>
       </c>
       <c r="Q42">
         <v>2.07</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
         <v>3.27</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V42">
         <v>1.49</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.18</v>
@@ -7194,19 +7194,19 @@
         <v>4</v>
       </c>
       <c r="AA42">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC42">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
         <v>1.63</v>
@@ -7321,28 +7321,28 @@
         <v>1.78</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="Q43">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R43">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W43">
         <v>1.17</v>
@@ -7351,31 +7351,31 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AA43">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB43">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AC43">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AD43">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG43">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
         <v>1.83</v>
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4.16</v>
       </c>
       <c r="P46">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q46">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="R46">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AC46">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE46">
+        <v>1.22</v>
+      </c>
+      <c r="AF46">
+        <v>1.6</v>
+      </c>
+      <c r="AG46">
+        <v>2.25</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.25</v>
       </c>
-      <c r="AF46">
-        <v>1.55</v>
-      </c>
-      <c r="AG46">
-        <v>2.3</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
+      <c r="AK46">
         <v>1.18</v>
-      </c>
-      <c r="AK46">
-        <v>1.12</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="O47">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="P47">
-        <v>7.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q47">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="R47">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T47">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U47">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V47">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="W47">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z47">
-        <v>6.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA47">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AB47">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AC47">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AD47">
         <v>1.7</v>
       </c>
       <c r="AE47">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK47">
         <v>2.5</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB48">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="R49">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S49">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V49">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W49">
         <v>1.18</v>
@@ -8332,7 +8332,7 @@
         <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA49">
         <v>1.45</v>
@@ -8347,13 +8347,13 @@
         <v>1.65</v>
       </c>
       <c r="AE49">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF49">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG49">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8794,25 +8794,25 @@
         <v>1.3</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -8839,10 +8839,10 @@
         <v>0</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,28 +8948,28 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P53">
         <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="R53">
         <v>1.93</v>
       </c>
       <c r="S53">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T53">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U53">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V53">
         <v>1.36</v>
@@ -8981,10 +8981,10 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z53">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="AA53">
         <v>1.88</v>
@@ -8993,19 +8993,19 @@
         <v>1.79</v>
       </c>
       <c r="AC53">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE53">
         <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG53">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,28 +9274,28 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="O55">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
       </c>
       <c r="R55">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S55">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T55">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="U55">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="V55">
         <v>1.38</v>
@@ -9313,16 +9313,16 @@
         <v>3.5</v>
       </c>
       <c r="AA55">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB55">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC55">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD55">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
         <v>1.06</v>
@@ -9331,7 +9331,7 @@
         <v>1.75</v>
       </c>
       <c r="AG55">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q57">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="S57">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="V57">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB57">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AC57">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AD57">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK57">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL57">
         <v>0</v>

--- a/jogos_2026-07-31.xlsx
+++ b/jogos_2026-07-31.xlsx
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "45+1"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O7">
-        <v>4.35</v>
+        <v>5.15</v>
       </c>
       <c r="P7">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T7">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="U7">
+        <v>2.2</v>
+      </c>
+      <c r="V7">
+        <v>1.6</v>
+      </c>
+      <c r="W7">
+        <v>1.14</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.13</v>
+      </c>
+      <c r="Z7">
+        <v>4.7</v>
+      </c>
+      <c r="AA7">
+        <v>1.57</v>
+      </c>
+      <c r="AB7">
+        <v>2.35</v>
+      </c>
+      <c r="AC7">
         <v>2.25</v>
       </c>
-      <c r="V7">
-        <v>1.57</v>
-      </c>
-      <c r="W7">
-        <v>1.1</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.16</v>
-      </c>
-      <c r="Z7">
-        <v>4</v>
-      </c>
-      <c r="AA7">
-        <v>1.67</v>
-      </c>
-      <c r="AB7">
-        <v>2.23</v>
-      </c>
-      <c r="AC7">
-        <v>2.66</v>
-      </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
         <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,37 +1520,37 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK7">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "31"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,11 +2420,11 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,23 +2571,23 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "28", "71", "83"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,66 +2722,66 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P15">
-        <v>3.22</v>
+        <v>1.91</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="R15">
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,29 +2790,29 @@
         <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA15">
+        <v>1.66</v>
+      </c>
+      <c r="AB15">
+        <v>2.15</v>
+      </c>
+      <c r="AC15">
+        <v>2.62</v>
+      </c>
+      <c r="AD15">
+        <v>1.4</v>
+      </c>
+      <c r="AE15">
+        <v>1.19</v>
+      </c>
+      <c r="AF15">
         <v>1.56</v>
       </c>
-      <c r="AB15">
-        <v>2.45</v>
-      </c>
-      <c r="AC15">
+      <c r="AG15">
         <v>2.28</v>
       </c>
-      <c r="AD15">
-        <v>1.6</v>
-      </c>
-      <c r="AE15">
-        <v>1.15</v>
-      </c>
-      <c r="AF15">
-        <v>1.47</v>
-      </c>
-      <c r="AG15">
-        <v>2.45</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2820,41 +2820,41 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "71", "89"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,25 +2885,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2913,38 +2913,38 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>3.55</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>1.91</v>
+        <v>3.22</v>
       </c>
       <c r="Q16">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="R16">
         <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V16">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2953,28 +2953,28 @@
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA16">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AC16">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE16">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AG16">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2983,41 +2983,41 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
+        <v>1.7</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>4</v>
+      </c>
+      <c r="AN16">
+        <v>5</v>
+      </c>
+      <c r="AO16">
+        <v>9</v>
+      </c>
+      <c r="AP16">
+        <v>8</v>
+      </c>
+      <c r="AQ16">
+        <v>1.49</v>
+      </c>
+      <c r="AR16">
         <v>1.21</v>
       </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1</v>
-      </c>
-      <c r="AN16">
-        <v>-1</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>-1</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
       <c r="AS16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "32", "37", "44", "72"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "60", "66"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3402,56 +3402,56 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>4.37</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>4.24</v>
+        <v>3.9</v>
       </c>
       <c r="AA19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD19">
         <v>1.4</v>
@@ -3463,7 +3463,7 @@
         <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,37 +3476,37 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,39 +3549,39 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="P20">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q20">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3590,7 +3590,7 @@
         <v>4</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
         <v>1.67</v>
@@ -3599,34 +3599,34 @@
         <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB20">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC20">
         <v>2.14</v>
       </c>
       <c r="AD20">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE20">
         <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3635,41 +3635,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "68", "83"]</t>
         </is>
       </c>
       <c r="AJ20">
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,130 +3709,130 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="O21">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="P21">
-        <v>8.56</v>
+        <v>7.25</v>
       </c>
       <c r="Q21">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="R21">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="S21">
         <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="U21">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="V21">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="W21">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA21">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AB21">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AC21">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="AE21">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AF21">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>["4", "9", "21", "54", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK21">
-        <v>5.15</v>
+        <v>4.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "74"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "52", "56", "90"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,26 +4035,26 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87", "90"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "56"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "29", "79"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4352,139 +4352,139 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R25">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T25">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U25">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA25">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC25">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG25">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "89"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK25">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4515,25 +4515,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4543,111 +4543,111 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P26">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z26">
-        <v>5.53</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AB26">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AC26">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AD26">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF26">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4678,63 +4678,63 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
         <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="Q27">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
         <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="T27">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
         <v>1.13</v>
@@ -4743,74 +4743,74 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>4.9</v>
+        <v>5.53</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AC27">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE27">
         <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
         <v>2.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "56"]</t>
         </is>
       </c>
       <c r="AJ27">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4853,23 +4853,23 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "61"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "52"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "65"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "57"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -6154,26 +6154,26 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P37">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q37">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
         <v>2.2</v>
@@ -6373,28 +6373,28 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB37">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AC37">
         <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE37">
         <v>1.23</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
         <v>2.05</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK37">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6634,22 +6634,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -6662,111 +6662,111 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
+        <v>2.34</v>
+      </c>
+      <c r="O39">
+        <v>3.25</v>
+      </c>
+      <c r="P39">
+        <v>2.65</v>
+      </c>
+      <c r="Q39">
+        <v>2.88</v>
+      </c>
+      <c r="R39">
+        <v>2.2</v>
+      </c>
+      <c r="S39">
+        <v>1.33</v>
+      </c>
+      <c r="T39">
+        <v>3.28</v>
+      </c>
+      <c r="U39">
         <v>2.45</v>
       </c>
-      <c r="O39">
-        <v>3.2</v>
-      </c>
-      <c r="P39">
-        <v>2.71</v>
-      </c>
-      <c r="Q39">
-        <v>2.78</v>
-      </c>
-      <c r="R39">
-        <v>2.06</v>
-      </c>
-      <c r="S39">
+      <c r="V39">
+        <v>1.47</v>
+      </c>
+      <c r="W39">
+        <v>1.06</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>3.85</v>
+      </c>
+      <c r="AA39">
+        <v>1.8</v>
+      </c>
+      <c r="AB39">
+        <v>2</v>
+      </c>
+      <c r="AC39">
+        <v>2.88</v>
+      </c>
+      <c r="AD39">
         <v>1.36</v>
       </c>
-      <c r="T39">
-        <v>2.7</v>
-      </c>
-      <c r="U39">
-        <v>2.88</v>
-      </c>
-      <c r="V39">
-        <v>1.36</v>
-      </c>
-      <c r="W39">
-        <v>1.07</v>
-      </c>
-      <c r="X39">
-        <v>1.05</v>
-      </c>
-      <c r="Y39">
-        <v>1.25</v>
-      </c>
-      <c r="Z39">
-        <v>3.3</v>
-      </c>
-      <c r="AA39">
-        <v>1.81</v>
-      </c>
-      <c r="AB39">
-        <v>1.8</v>
-      </c>
-      <c r="AC39">
-        <v>3.45</v>
-      </c>
-      <c r="AD39">
+      <c r="AE39">
+        <v>1.1</v>
+      </c>
+      <c r="AF39">
+        <v>1.57</v>
+      </c>
+      <c r="AG39">
+        <v>2.2</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>["32"]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.22</v>
+      </c>
+      <c r="AK39">
+        <v>1.47</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>1</v>
+      </c>
+      <c r="AN39">
+        <v>4</v>
+      </c>
+      <c r="AO39">
+        <v>7</v>
+      </c>
+      <c r="AP39">
+        <v>9</v>
+      </c>
+      <c r="AQ39">
+        <v>0.8</v>
+      </c>
+      <c r="AR39">
         <v>1.3</v>
       </c>
-      <c r="AE39">
-        <v>1.11</v>
-      </c>
-      <c r="AF39">
-        <v>1.7</v>
-      </c>
-      <c r="AG39">
-        <v>2.01</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.35</v>
-      </c>
-      <c r="AK39">
-        <v>1.53</v>
-      </c>
-      <c r="AL39">
-        <v>0</v>
-      </c>
-      <c r="AM39">
-        <v>-1</v>
-      </c>
-      <c r="AN39">
-        <v>-1</v>
-      </c>
-      <c r="AO39">
-        <v>-1</v>
-      </c>
-      <c r="AP39">
-        <v>-1</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
       <c r="AS39">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6797,19 +6797,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6821,115 +6821,115 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>2.34</v>
+        <v>9.5</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>7.74</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="S40">
         <v>1.33</v>
       </c>
       <c r="T40">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V40">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB40">
+        <v>2.1</v>
+      </c>
+      <c r="AC40">
+        <v>2.58</v>
+      </c>
+      <c r="AD40">
+        <v>1.46</v>
+      </c>
+      <c r="AE40">
+        <v>1.13</v>
+      </c>
+      <c r="AF40">
+        <v>1.97</v>
+      </c>
+      <c r="AG40">
+        <v>1.83</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>["67", "89", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>2.6</v>
+      </c>
+      <c r="AK40">
+        <v>1.01</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
         <v>2</v>
       </c>
-      <c r="AC40">
-        <v>2.88</v>
-      </c>
-      <c r="AD40">
-        <v>1.36</v>
-      </c>
-      <c r="AE40">
-        <v>1.1</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
-      <c r="AG40">
-        <v>2.2</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.22</v>
-      </c>
-      <c r="AK40">
-        <v>1.47</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6960,25 +6960,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -6988,68 +6988,68 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>9.5</v>
+        <v>2.45</v>
       </c>
       <c r="O41">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="Q41">
-        <v>7.74</v>
+        <v>2.78</v>
       </c>
       <c r="R41">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
+        <v>1.05</v>
+      </c>
+      <c r="Y41">
+        <v>1.25</v>
+      </c>
+      <c r="Z41">
+        <v>3.3</v>
+      </c>
+      <c r="AA41">
+        <v>1.81</v>
+      </c>
+      <c r="AB41">
+        <v>1.8</v>
+      </c>
+      <c r="AC41">
+        <v>3.45</v>
+      </c>
+      <c r="AD41">
+        <v>1.3</v>
+      </c>
+      <c r="AE41">
         <v>1.11</v>
       </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.18</v>
-      </c>
-      <c r="Z41">
-        <v>3.1</v>
-      </c>
-      <c r="AA41">
-        <v>1.57</v>
-      </c>
-      <c r="AB41">
-        <v>2.1</v>
-      </c>
-      <c r="AC41">
-        <v>2.58</v>
-      </c>
-      <c r="AD41">
-        <v>1.46</v>
-      </c>
-      <c r="AE41">
-        <v>1.13</v>
-      </c>
       <c r="AF41">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7058,41 +7058,41 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="AK41">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7135,23 +7135,23 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "57", "78", "80"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q44">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
         <v>1.36</v>
@@ -7508,37 +7508,37 @@
         <v>1.37</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA44">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC44">
-        <v>3.57</v>
+        <v>3.18</v>
       </c>
       <c r="AD44">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
         <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O45">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="P45">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="Q45">
         <v>1.57</v>
       </c>
       <c r="R45">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="S45">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T45">
         <v>4.75</v>
       </c>
       <c r="U45">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="V45">
         <v>1.85</v>
       </c>
       <c r="W45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>6.4</v>
+        <v>6.85</v>
       </c>
       <c r="AA45">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AB45">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="AC45">
         <v>1.78</v>
       </c>
       <c r="AD45">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF45">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK45">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7784,13 +7784,13 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -7799,11 +7799,11 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -8465,22 +8465,22 @@
         <v>4</v>
       </c>
       <c r="P50">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q50">
         <v>2.06</v>
       </c>
       <c r="R50">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
         <v>1.5</v>
@@ -8489,47 +8489,47 @@
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z50">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD50">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
+        <v>1.17</v>
+      </c>
+      <c r="AF50">
+        <v>1.67</v>
+      </c>
+      <c r="AG50">
+        <v>2.06</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.16</v>
-      </c>
-      <c r="AF50">
-        <v>1.68</v>
-      </c>
-      <c r="AG50">
-        <v>2.05</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.15</v>
       </c>
       <c r="AK50">
         <v>2.2</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="Q51">
         <v>3.05</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.65</v>
       </c>
       <c r="V51">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
         <v>1.08</v>
@@ -8661,13 +8661,13 @@
         <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AC51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
@@ -9114,16 +9114,16 @@
         <v>2.33</v>
       </c>
       <c r="O54">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="P54">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q54">
         <v>2.3</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S54">
         <v>1.3</v>
@@ -9132,43 +9132,43 @@
         <v>3.1</v>
       </c>
       <c r="U54">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="AA54">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB54">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC54">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD54">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="O56">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="Q56">
         <v>2.5</v>
       </c>
       <c r="R56">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="V56">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA56">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB56">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AC56">
-        <v>3.15</v>
+        <v>2.52</v>
       </c>
       <c r="AD56">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AE56">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF56">
+        <v>1.53</v>
+      </c>
+      <c r="AG56">
+        <v>2.08</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.2</v>
+      </c>
+      <c r="AK56">
         <v>1.7</v>
-      </c>
-      <c r="AG56">
-        <v>2</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.22</v>
-      </c>
-      <c r="AK56">
-        <v>1.8</v>
       </c>
       <c r="AL56">
         <v>0</v>
